--- a/基本設計/00_基本設計書総合管理.xlsx
+++ b/基本設計/00_基本設計書総合管理.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6c9ee968fe88458f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R54e2566d93aa4795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="Rfbe7001979514799"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="Rb49ee706a689487d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="R133c11d28a404135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="Rd84dc6454e594066"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R8bfa01937aba4d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rbbf1dd3add4f464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R177910a6e43f4bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R811cfad56b5c41bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="R7e4721b80ff04108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="Rabe9da20977d4adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R3c1163c920194373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R555ec30c22704395"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1367,10 +1367,7 @@
       <x:c r="F16" s="222"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1386,25 +1383,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="264" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="264"/>
-      <x:c r="D19" s="264"/>
-      <x:c r="E19" s="264"/>
-      <x:c r="F19" s="264"/>
-      <x:c r="G19" s="264"/>
-      <x:c r="H19" s="264"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="264"/>
-      <x:c r="C20" s="264"/>
-      <x:c r="D20" s="264"/>
-      <x:c r="E20" s="264"/>
-      <x:c r="F20" s="264"/>
-      <x:c r="G20" s="264"/>
-      <x:c r="H20" s="264"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="264"/>

--- a/基本設計/00_基本設計書総合管理.xlsx
+++ b/基本設計/00_基本設計書総合管理.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rbbf1dd3add4f464a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R177910a6e43f4bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R811cfad56b5c41bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="R7e4721b80ff04108"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="Rabe9da20977d4adb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R3c1163c920194373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R555ec30c22704395"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R0324d1e50c29418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Re058c3dbba404a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R6be70d4c6283460a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="R6a8b729516014b5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="R30e057ef1fec4d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="Rf4afefcdf14144ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R03ecfeec461349ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="R12aab8f26d2240b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -161,8 +162,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="35">
+  <x:fills count="38">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -334,8 +346,23 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -393,11 +420,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="265">
+  <x:cellXfs count="289">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -935,6 +976,74 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="37" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="37" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1235,7 +1344,36 @@
     <x:col min="26" max="26" width="3" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1"/>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
     <x:row r="3">
+      <x:c r="A3"/>
       <x:c r="B3" s="251" t="str">
         <x:v>Company WorkHub
 企業従業員・タスク管理システム</x:v>
@@ -1246,8 +1384,13 @@
       <x:c r="F3" s="251"/>
       <x:c r="G3" s="251"/>
       <x:c r="H3" s="251"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4"/>
       <x:c r="B4" s="251"/>
       <x:c r="C4" s="251"/>
       <x:c r="D4" s="251"/>
@@ -1255,8 +1398,13 @@
       <x:c r="F4" s="251"/>
       <x:c r="G4" s="251"/>
       <x:c r="H4" s="251"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5"/>
       <x:c r="B5" s="251"/>
       <x:c r="C5" s="251"/>
       <x:c r="D5" s="251"/>
@@ -1264,8 +1412,13 @@
       <x:c r="F5" s="251"/>
       <x:c r="G5" s="251"/>
       <x:c r="H5" s="251"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6"/>
       <x:c r="B6"/>
       <x:c r="C6"/>
       <x:c r="D6"/>
@@ -1273,8 +1426,27 @@
       <x:c r="F6"/>
       <x:c r="G6"/>
       <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
+      <x:c r="A8"/>
       <x:c r="B8" s="257" t="str">
         <x:v>基本設計書総合管理</x:v>
       </x:c>
@@ -1284,8 +1456,13 @@
       <x:c r="F8" s="257"/>
       <x:c r="G8" s="257"/>
       <x:c r="H8" s="257"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
+      <x:c r="A9"/>
       <x:c r="B9" s="257"/>
       <x:c r="C9" s="257"/>
       <x:c r="D9" s="257"/>
@@ -1293,8 +1470,13 @@
       <x:c r="F9" s="257"/>
       <x:c r="G9" s="257"/>
       <x:c r="H9" s="257"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
+      <x:c r="A10"/>
       <x:c r="B10" s="257"/>
       <x:c r="C10" s="257"/>
       <x:c r="D10" s="257"/>
@@ -1302,49 +1484,84 @@
       <x:c r="F10" s="257"/>
       <x:c r="G10" s="257"/>
       <x:c r="H10" s="257"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
+      <x:c r="A11"/>
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="265" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
       <x:c r="F11"/>
       <x:c r="G11"/>
       <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="259" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12" s="269" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="222" t="str">
         <x:v>CW-BD-MGT</x:v>
       </x:c>
       <x:c r="E12" s="222"/>
       <x:c r="F12" s="222"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
       <x:c r="C13" s="259" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="222" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="270" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="222"/>
       <x:c r="F13" s="222"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
       <x:c r="C14" s="259" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="222" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="270" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="222"/>
       <x:c r="F14" s="222"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
       <x:c r="C15" s="259" t="str">
         <x:v>作成者</x:v>
       </x:c>
@@ -1353,6 +1570,12 @@
       </x:c>
       <x:c r="E15" s="222"/>
       <x:c r="F15" s="222"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
@@ -1360,24 +1583,35 @@
       <x:c r="C16" s="259" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="222" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="270" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="222"/>
       <x:c r="F16" s="222"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="272"/>
+      <x:c r="B17" s="272"/>
+      <x:c r="C17" s="272"/>
+      <x:c r="D17" s="272"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="272"/>
+      <x:c r="B18" s="272"/>
+      <x:c r="C18" s="272" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="272" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1474,6 +1708,10 @@
       <x:c r="F1" s="198"/>
       <x:c r="G1" s="198"/>
       <x:c r="H1" s="198"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="198"/>
@@ -1484,42 +1722,42 @@
       <x:c r="F2" s="198"/>
       <x:c r="G2" s="198"/>
       <x:c r="H2" s="198"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="200" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="160" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="160"/>
-      <x:c r="D3" s="200" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="160" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="160"/>
-      <x:c r="G3" s="160"/>
-      <x:c r="H3" s="160"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="200" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="160" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="160"/>
-      <x:c r="D4" s="200" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="160" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="160"/>
-      <x:c r="G4" s="160"/>
-      <x:c r="H4" s="160"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="275" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="72"/>
+      <x:c r="C3" s="72"/>
+      <x:c r="D3" s="275"/>
+      <x:c r="E3" s="72"/>
+      <x:c r="F3" s="72"/>
+      <x:c r="G3" s="72"/>
+      <x:c r="H3" s="72"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="275" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="72"/>
+      <x:c r="C4" s="72"/>
+      <x:c r="D4" s="275"/>
+      <x:c r="E4" s="72"/>
+      <x:c r="F4" s="72"/>
+      <x:c r="G4" s="72"/>
+      <x:c r="H4" s="72"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1530,6 +1768,10 @@
       <x:c r="F5"/>
       <x:c r="G5"/>
       <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="201" t="str">
@@ -1542,6 +1784,10 @@
       <x:c r="F6" s="201"/>
       <x:c r="G6" s="201"/>
       <x:c r="H6" s="201"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="207" t="str">
@@ -1551,7 +1797,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="207" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="207" t="str">
         <x:v>作成者</x:v>
@@ -1568,6 +1814,10 @@
       <x:c r="H7" s="207" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="76" t="str">
@@ -1589,11 +1839,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="76" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="76" t="str">
         <x:v>基本設計初版</x:v>
       </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="76" t="str">
@@ -1615,11 +1869,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="76" t="str">
         <x:v>Leader Review後Baseline化</x:v>
       </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="76" t="str">
@@ -1641,11 +1899,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="76" t="str">
         <x:v>Review指摘対応</x:v>
       </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="76" t="str">
@@ -1667,11 +1929,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="76" t="str">
         <x:v>再監査指摘対応</x:v>
       </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="76" t="str">
@@ -1693,11 +1959,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="76" t="str">
         <x:v>再監査第2回指摘対応</x:v>
       </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -1718,12 +1988,16 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="265" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
       </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -1744,12 +2018,16 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="265" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
       </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -1770,25 +2048,213 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="265" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>認証・ホーム画面遷移、Dashboard集計Rule、通知Header責務を整合</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" s="265" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>04再Review指摘対応</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>七項目Review指摘対応：画面・API・DB項目、論理削除、認証限流、日報関連Task、Baseline判定を整合</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>レビュー済</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Leader最終承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>第1回従業員・部門業務仕様Review指摘対応をBaselineへ反映</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="265" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>第1回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>第2回業務仕様Review：従業員・部門の残存Major/Minorを整合</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G19" s="265" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>第2回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="110" customHeight="1">
+      <x:c r="A20" s="266" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B20" s="266" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C20" s="266" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D20" s="266" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E20" s="266" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F20" s="266" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G20" s="266" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H20" s="266" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="40" customHeight="1">
+      <x:c r="A21" s="266" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B21" s="266" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C21" s="266" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D21" s="266" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E21" s="266" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F21" s="266" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G21" s="266" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H21" s="266" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I21" s="266"/>
+      <x:c r="J21" s="266"/>
+      <x:c r="K21" s="266"/>
+      <x:c r="L21" s="266"/>
+    </x:row>
+    <x:row r="22" ht="100" customHeight="1">
+      <x:c r="A22" s="272" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B22" s="272" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C22" s="272" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。 Batch起動排他の正式化、Rule追跡・通知Template正本の整合。</x:v>
+      </x:c>
+      <x:c r="D22" s="272" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E22" s="272" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F22" s="272" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G22" s="272" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H22" s="272" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1815,6 +2281,12 @@
       <x:c r="D1" s="20"/>
       <x:c r="E1" s="20"/>
       <x:c r="F1" s="20"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20"/>
@@ -1823,6 +2295,12 @@
       <x:c r="D2" s="20"/>
       <x:c r="E2" s="20"/>
       <x:c r="F2" s="20"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="23" t="str">
@@ -1833,30 +2311,50 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="273" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
-      <x:c r="G3" t="str">
-        <x:v>CW-BD-003</x:v>
-      </x:c>
+      <x:c r="G3" t="str"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
+      <x:c r="A4" s="273" t="str">
+        <x:v>版数：Ver.2.5</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="274" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
+      <x:c r="E4" s="273" t="str">
+        <x:v>作成日：2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="35"/>
-      <x:c r="G4" s="36" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="36"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -1867,6 +2365,12 @@
       <x:c r="D6" s="26"/>
       <x:c r="E6" s="26"/>
       <x:c r="F6" s="26"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
@@ -1887,6 +2391,12 @@
       <x:c r="F7" s="31" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33" t="n">
@@ -1904,7 +2414,13 @@
       <x:c r="E8" s="33" t="str">
         <x:v>全体</x:v>
       </x:c>
-      <x:c r="F8" s="33" t="str"/>
+      <x:c r="F8" s="33"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33" t="n">
@@ -1922,7 +2438,13 @@
       <x:c r="E9" s="33" t="str">
         <x:v>M05/M06/M07</x:v>
       </x:c>
-      <x:c r="F9" s="33" t="str"/>
+      <x:c r="F9" s="33"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33" t="n">
@@ -1940,7 +2462,13 @@
       <x:c r="E10" s="33" t="str">
         <x:v>M06/M07</x:v>
       </x:c>
-      <x:c r="F10" s="33" t="str"/>
+      <x:c r="F10" s="33"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33" t="n">
@@ -1958,7 +2486,13 @@
       <x:c r="E11" s="33" t="str">
         <x:v>M01</x:v>
       </x:c>
-      <x:c r="F11" s="33" t="str"/>
+      <x:c r="F11" s="33"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33" t="n">
@@ -1974,9 +2508,15 @@
         <x:v>Access Token再発行用。Redisで7日保持</x:v>
       </x:c>
       <x:c r="E12" s="33" t="str">
-        <x:v>M01/M35</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str"/>
+        <x:v>M01。関連設計：19／35_Redis</x:v>
+      </x:c>
+      <x:c r="F12" s="33"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33" t="n">
@@ -1994,7 +2534,13 @@
       <x:c r="E13" s="33" t="str">
         <x:v>データ設計</x:v>
       </x:c>
-      <x:c r="F13" s="33" t="str"/>
+      <x:c r="F13" s="33"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33" t="n">
@@ -2012,7 +2558,13 @@
       <x:c r="E14" s="33" t="str">
         <x:v>更新処理</x:v>
       </x:c>
-      <x:c r="F14" s="33" t="str"/>
+      <x:c r="F14" s="33"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33" t="n">
@@ -2030,7 +2582,13 @@
       <x:c r="E15" s="33" t="str">
         <x:v>登録API</x:v>
       </x:c>
-      <x:c r="F15" s="33" t="str"/>
+      <x:c r="F15" s="33"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33" t="n">
@@ -2049,8 +2607,14 @@
         <x:v>M07</x:v>
       </x:c>
       <x:c r="F16" s="33" t="str">
-        <x:v>同一社員・同一日一件</x:v>
-      </x:c>
+        <x:v>同一社員・同一PJ・同一日一件</x:v>
+      </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33" t="n">
@@ -2102,7 +2666,7 @@
         <x:v>単体テストの実行条件と結果を示す画像・ログ等</x:v>
       </x:c>
       <x:c r="E19" s="33" t="str">
-        <x:v>教学配套</x:v>
+        <x:v>研修用資料</x:v>
       </x:c>
       <x:c r="F19" s="33" t="str"/>
     </x:row>
@@ -2115,9 +2679,8 @@
     <x:mergeCell ref="F3:G3"/>
     <x:mergeCell ref="A4:B4"/>
     <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="A6:F6"/>
+    <x:mergeCell ref="E4:G4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2144,6 +2707,12 @@
       <x:c r="D1" s="198"/>
       <x:c r="E1" s="198"/>
       <x:c r="F1" s="198"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="198"/>
@@ -2152,40 +2721,48 @@
       <x:c r="D2" s="198"/>
       <x:c r="E2" s="198"/>
       <x:c r="F2" s="198"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="200" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="160" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="200" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D3" s="160" t="str">
-        <x:v>CW-BD-004</x:v>
-      </x:c>
+      <x:c r="B3" s="160" t="str"/>
+      <x:c r="C3" s="275" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="D3" s="160" t="str"/>
       <x:c r="E3" s="160"/>
       <x:c r="F3" s="160"/>
       <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="200" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="160" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="200" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="D4" s="160" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="A4" s="275" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="160"/>
+      <x:c r="C4" s="275" t="str">
+        <x:v>改訂日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="D4" s="160"/>
       <x:c r="E4" s="160"/>
       <x:c r="F4" s="160"/>
       <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -2194,16 +2771,28 @@
       <x:c r="D5"/>
       <x:c r="E5"/>
       <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="201" t="str">
-        <x:v>1. 確定前提条件</x:v>
+        <x:v>1. 前提条件</x:v>
       </x:c>
       <x:c r="B6" s="201"/>
       <x:c r="C6" s="201"/>
       <x:c r="D6" s="201"/>
       <x:c r="E6" s="201"/>
       <x:c r="F6" s="201"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="207" t="str">
@@ -2224,6 +2813,12 @@
       <x:c r="F7" s="207" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="76" t="n">
@@ -2242,6 +2837,12 @@
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F8" s="76"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="76" t="n">
@@ -2260,6 +2861,12 @@
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F9" s="76"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="76" t="n">
@@ -2278,6 +2885,12 @@
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F10" s="76"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="76" t="n">
@@ -2296,6 +2909,12 @@
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F11" s="76"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="76" t="n">
@@ -2314,6 +2933,12 @@
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F12" s="76"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="76" t="n">
@@ -2332,6 +2957,12 @@
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F13" s="76"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="76" t="n">
@@ -2352,6 +2983,12 @@
       <x:c r="F14" s="76" t="str">
         <x:v>両方式の混在は画面単位で禁止</x:v>
       </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="76" t="n">
@@ -2370,6 +3007,12 @@
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F15" s="76"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="76" t="n">
@@ -2390,6 +3033,12 @@
       <x:c r="F16" s="76" t="str">
         <x:v>自動Queueは使用しない</x:v>
       </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="76" t="n">
@@ -2409,7 +3058,7 @@
       </x:c>
       <x:c r="F17" s="76"/>
     </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+    <x:row r="18" ht="40" customHeight="1">
       <x:c r="A18" s="76" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -2417,15 +3066,21 @@
         <x:v>性能</x:v>
       </x:c>
       <x:c r="C18" s="76" t="str">
-        <x:v>同時Online100人、API 50req/s以上</x:v>
+        <x:v>性能測定目標：同時Online100人、API 50req/s。硬性合否条件ではない。</x:v>
       </x:c>
       <x:c r="D18" s="76" t="str">
-        <x:v>性能・結合試験へ反映</x:v>
+        <x:v>20／38の条件で実測し、未達は原因と改善案を記録。</x:v>
       </x:c>
       <x:c r="E18" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
       <x:c r="F18" s="76"/>
+      <x:c r="G18" s="266"/>
+      <x:c r="H18" s="266"/>
+      <x:c r="I18" s="266"/>
+      <x:c r="J18" s="266"/>
+      <x:c r="K18" s="266"/>
+      <x:c r="L18" s="266"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="76" t="n">
@@ -2541,35 +3196,333 @@
         <x:v>BATCH-003の営業日判定Source</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="212" t="str">
-        <x:v>本表の「確定」を基本設計Baselineとし、変更は課題票とProject Leader承認を必要とする。</x:v>
-      </x:c>
-      <x:c r="B26" s="212"/>
-      <x:c r="C26" s="212"/>
-      <x:c r="D26" s="212"/>
-      <x:c r="E26" s="212"/>
-      <x:c r="F26" s="212"/>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="265" t="str">
+        <x:v>変更は課題票とProject Leader承認を必要とする。</x:v>
+      </x:c>
+      <x:c r="B25" s="265"/>
+      <x:c r="C25" s="265"/>
+      <x:c r="D25" s="265"/>
+      <x:c r="E25" s="265"/>
+      <x:c r="F25" s="265"/>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="288" t="str">
+        <x:v>2. 設計正本参照事項</x:v>
+      </x:c>
+      <x:c r="B26" s="288"/>
+      <x:c r="C26" s="288"/>
+      <x:c r="D26" s="288"/>
+      <x:c r="E26" s="288"/>
+      <x:c r="F26" s="288"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="212" t="n">
+      <x:c r="A27" s="288" t="str">
+        <x:v>No.</x:v>
+      </x:c>
+      <x:c r="B27" s="288" t="str">
+        <x:v>設計事項</x:v>
+      </x:c>
+      <x:c r="C27" s="288" t="str">
+        <x:v>参照先</x:v>
+      </x:c>
+      <x:c r="D27" s="288" t="str">
+        <x:v>正本</x:v>
+      </x:c>
+      <x:c r="E27" s="288" t="str">
+        <x:v>確認状態</x:v>
+      </x:c>
+      <x:c r="F27" s="288" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="40" customHeight="1">
+      <x:c r="A28" s="266" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B27" s="212" t="str">
-        <x:v>業務決定</x:v>
-      </x:c>
-      <x:c r="C27" s="212" t="str">
-        <x:v>日報は社員・PJ・日単位で1件。Employee/Role状態変更は専用状態APIのみ使用</x:v>
-      </x:c>
-      <x:c r="D27" s="212" t="str">
-        <x:v>詳細設計・DB Unique・画面Eventを統一</x:v>
-      </x:c>
-      <x:c r="E27" s="212" t="str">
-        <x:v>確定</x:v>
-      </x:c>
-      <x:c r="F27" s="212" t="str">
-        <x:v>Excel取込は部分成功方式。通知保持はread_at基準</x:v>
-      </x:c>
+      <x:c r="B28" s="266" t="str">
+        <x:v>日報日次合計</x:v>
+      </x:c>
+      <x:c r="C28" s="266" t="str">
+        <x:v>正本参照：16／28 BR-RPT-004</x:v>
+      </x:c>
+      <x:c r="D28" s="266" t="str">
+        <x:v>16／28 BR-RPT-004</x:v>
+      </x:c>
+      <x:c r="E28" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F28" s="266" t="str"/>
+      <x:c r="G28" s="266"/>
+      <x:c r="H28" s="266"/>
+      <x:c r="I28" s="266"/>
+      <x:c r="J28" s="266"/>
+      <x:c r="K28" s="266"/>
+      <x:c r="L28" s="266"/>
+    </x:row>
+    <x:row r="29" ht="54" customHeight="1">
+      <x:c r="A29" s="266" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B29" s="266" t="str">
+        <x:v>RoleとData範囲</x:v>
+      </x:c>
+      <x:c r="C29" s="266" t="str">
+        <x:v>正本参照：02／09・14</x:v>
+      </x:c>
+      <x:c r="D29" s="266" t="str">
+        <x:v>02／09・14</x:v>
+      </x:c>
+      <x:c r="E29" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F29" s="266" t="str"/>
+      <x:c r="G29" s="266"/>
+      <x:c r="H29" s="266"/>
+      <x:c r="I29" s="266"/>
+      <x:c r="J29" s="266"/>
+      <x:c r="K29" s="266"/>
+      <x:c r="L29" s="266"/>
+    </x:row>
+    <x:row r="30" ht="54" customHeight="1">
+      <x:c r="A30" s="266" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B30" s="266" t="str">
+        <x:v>PJ状態</x:v>
+      </x:c>
+      <x:c r="C30" s="266" t="str">
+        <x:v>正本参照：16／27</x:v>
+      </x:c>
+      <x:c r="D30" s="266" t="str">
+        <x:v>16／27</x:v>
+      </x:c>
+      <x:c r="E30" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F30" s="266" t="str"/>
+      <x:c r="G30" s="266"/>
+      <x:c r="H30" s="266"/>
+      <x:c r="I30" s="266"/>
+      <x:c r="J30" s="266"/>
+      <x:c r="K30" s="266"/>
+      <x:c r="L30" s="266"/>
+    </x:row>
+    <x:row r="31" ht="54" customHeight="1">
+      <x:c r="A31" s="266" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B31" s="266" t="str">
+        <x:v>Member/PM</x:v>
+      </x:c>
+      <x:c r="C31" s="266" t="str">
+        <x:v>正本参照：16／28 BR-MEM-001・003</x:v>
+      </x:c>
+      <x:c r="D31" s="266" t="str">
+        <x:v>16／28 BR-MEM-001・003</x:v>
+      </x:c>
+      <x:c r="E31" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F31" s="266" t="str"/>
+      <x:c r="G31" s="266"/>
+      <x:c r="H31" s="266"/>
+      <x:c r="I31" s="266"/>
+      <x:c r="J31" s="266"/>
+      <x:c r="K31" s="266"/>
+      <x:c r="L31" s="266"/>
+    </x:row>
+    <x:row r="32" ht="40" customHeight="1">
+      <x:c r="A32" s="266" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B32" s="266" t="str">
+        <x:v>Task進捗</x:v>
+      </x:c>
+      <x:c r="C32" s="266" t="str">
+        <x:v>正本参照：16／26・27</x:v>
+      </x:c>
+      <x:c r="D32" s="266" t="str">
+        <x:v>16／26・27</x:v>
+      </x:c>
+      <x:c r="E32" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F32" s="266" t="str"/>
+      <x:c r="G32" s="266"/>
+      <x:c r="H32" s="266"/>
+      <x:c r="I32" s="266"/>
+      <x:c r="J32" s="266"/>
+      <x:c r="K32" s="266"/>
+      <x:c r="L32" s="266"/>
+    </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" s="266" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B33" s="266" t="str">
+        <x:v>PJ/Task期間</x:v>
+      </x:c>
+      <x:c r="C33" s="266" t="str">
+        <x:v>正本参照：16／28 BR-TASK-002</x:v>
+      </x:c>
+      <x:c r="D33" s="266" t="str">
+        <x:v>16／28 BR-TASK-002</x:v>
+      </x:c>
+      <x:c r="E33" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F33" s="266" t="str"/>
+      <x:c r="G33" s="266"/>
+      <x:c r="H33" s="266"/>
+      <x:c r="I33" s="266"/>
+      <x:c r="J33" s="266"/>
+      <x:c r="K33" s="266"/>
+      <x:c r="L33" s="266"/>
+    </x:row>
+    <x:row r="34" ht="54" customHeight="1">
+      <x:c r="A34" s="266" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B34" s="266" t="str">
+        <x:v>日報未提出</x:v>
+      </x:c>
+      <x:c r="C34" s="266" t="str">
+        <x:v>正本参照：16／28 BR-RPT-005</x:v>
+      </x:c>
+      <x:c r="D34" s="266" t="str">
+        <x:v>16／28 BR-RPT-005</x:v>
+      </x:c>
+      <x:c r="E34" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F34" s="266" t="str"/>
+      <x:c r="G34" s="266"/>
+      <x:c r="H34" s="266"/>
+      <x:c r="I34" s="266"/>
+      <x:c r="J34" s="266"/>
+      <x:c r="K34" s="266"/>
+      <x:c r="L34" s="266"/>
+    </x:row>
+    <x:row r="35" ht="40" customHeight="1">
+      <x:c r="A35" s="266" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B35" s="266" t="str">
+        <x:v>日報削除後</x:v>
+      </x:c>
+      <x:c r="C35" s="266" t="str">
+        <x:v>正本参照：16／28 BR-RPT-001、15／08_FK・Constraint</x:v>
+      </x:c>
+      <x:c r="D35" s="266" t="str">
+        <x:v>16／28 BR-RPT-001、15／08_FK・Constraint</x:v>
+      </x:c>
+      <x:c r="E35" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F35" s="266" t="str"/>
+      <x:c r="G35" s="266"/>
+      <x:c r="H35" s="266"/>
+      <x:c r="I35" s="266"/>
+      <x:c r="J35" s="266"/>
+      <x:c r="K35" s="266"/>
+      <x:c r="L35" s="266"/>
+    </x:row>
+    <x:row r="36" ht="54" customHeight="1">
+      <x:c r="A36" s="266" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B36" s="266" t="str">
+        <x:v>秘密値と冪等</x:v>
+      </x:c>
+      <x:c r="C36" s="266" t="str">
+        <x:v>正本参照：16／28 BR-API-002、18／32</x:v>
+      </x:c>
+      <x:c r="D36" s="266" t="str">
+        <x:v>16／28 BR-API-002、18／32</x:v>
+      </x:c>
+      <x:c r="E36" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F36" s="266" t="str"/>
+      <x:c r="G36" s="266"/>
+      <x:c r="H36" s="266"/>
+      <x:c r="I36" s="266"/>
+      <x:c r="J36" s="266"/>
+      <x:c r="K36" s="266"/>
+      <x:c r="L36" s="266"/>
+    </x:row>
+    <x:row r="37" ht="54" customHeight="1">
+      <x:c r="A37" s="266" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B37" s="266" t="str">
+        <x:v>通知</x:v>
+      </x:c>
+      <x:c r="C37" s="266" t="str">
+        <x:v>正本参照：16／28 BR-NTF-002・003、20／37</x:v>
+      </x:c>
+      <x:c r="D37" s="266" t="str">
+        <x:v>16／28 BR-NTF-002・003、20／37</x:v>
+      </x:c>
+      <x:c r="E37" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F37" s="266" t="str"/>
+      <x:c r="G37" s="266"/>
+      <x:c r="H37" s="266"/>
+      <x:c r="I37" s="266"/>
+      <x:c r="J37" s="266"/>
+      <x:c r="K37" s="266"/>
+      <x:c r="L37" s="266"/>
+    </x:row>
+    <x:row r="38" ht="40" customHeight="1">
+      <x:c r="A38" s="266" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B38" s="266" t="str">
+        <x:v>日報統計Menu</x:v>
+      </x:c>
+      <x:c r="C38" s="266" t="str">
+        <x:v>正本参照：02／10、01／06</x:v>
+      </x:c>
+      <x:c r="D38" s="266" t="str">
+        <x:v>02／10、01／06</x:v>
+      </x:c>
+      <x:c r="E38" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F38" s="266" t="str"/>
+      <x:c r="G38" s="266"/>
+      <x:c r="H38" s="266"/>
+      <x:c r="I38" s="266"/>
+      <x:c r="J38" s="266"/>
+      <x:c r="K38" s="266"/>
+      <x:c r="L38" s="266"/>
+    </x:row>
+    <x:row r="39" ht="40" customHeight="1">
+      <x:c r="A39" s="266" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B39" s="266" t="str">
+        <x:v>非機能目標</x:v>
+      </x:c>
+      <x:c r="C39" s="266" t="str">
+        <x:v>正本参照：20／38・39</x:v>
+      </x:c>
+      <x:c r="D39" s="266" t="str">
+        <x:v>20／38・39</x:v>
+      </x:c>
+      <x:c r="E39" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F39" s="266" t="str"/>
+      <x:c r="G39" s="266"/>
+      <x:c r="H39" s="266"/>
+      <x:c r="I39" s="266"/>
+      <x:c r="J39" s="266"/>
+      <x:c r="K39" s="266"/>
+      <x:c r="L39" s="266"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2583,7 +3536,8 @@
     <x:mergeCell ref="E4:F4"/>
     <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A26:F27"/>
+    <x:mergeCell ref="A25:F25"/>
+    <x:mergeCell ref="A26:F26"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2593,773 +3547,837 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="54" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="198" t="str">
-        <x:v>基本設計書 文書一覧</x:v>
-      </x:c>
-      <x:c r="B1" s="198"/>
-      <x:c r="C1" s="198"/>
-      <x:c r="D1" s="198"/>
-      <x:c r="E1" s="198"/>
-      <x:c r="F1" s="198"/>
-      <x:c r="G1" s="198"/>
-      <x:c r="H1" s="198"/>
+      <x:c r="A1" s="279" t="str">
+        <x:v>02_文書一覧</x:v>
+      </x:c>
+      <x:c r="B1" s="278"/>
+      <x:c r="C1" s="278"/>
+      <x:c r="D1" s="278"/>
+      <x:c r="E1" s="278"/>
+      <x:c r="F1" s="278"/>
+      <x:c r="G1" s="278"/>
+      <x:c r="H1" s="278"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="198"/>
-      <x:c r="B2" s="198"/>
-      <x:c r="C2" s="198"/>
-      <x:c r="D2" s="198"/>
-      <x:c r="E2" s="198"/>
-      <x:c r="F2" s="198"/>
-      <x:c r="G2" s="198"/>
-      <x:c r="H2" s="198"/>
+      <x:c r="A2" s="278"/>
+      <x:c r="B2" s="278"/>
+      <x:c r="C2" s="278"/>
+      <x:c r="D2" s="278"/>
+      <x:c r="E2" s="278"/>
+      <x:c r="F2" s="278"/>
+      <x:c r="G2" s="278"/>
+      <x:c r="H2" s="278"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="200" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="160" t="str">
+      <x:c r="A3" s="278" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="160"/>
-      <x:c r="D3" s="200" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="160" t="str">
+      <x:c r="B3" s="278"/>
+      <x:c r="C3" s="278"/>
+      <x:c r="D3" s="278"/>
+      <x:c r="E3" s="278"/>
+      <x:c r="F3" s="278"/>
+      <x:c r="G3" s="278"/>
+      <x:c r="H3" s="278"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="278"/>
+      <x:c r="B4" s="278"/>
+      <x:c r="C4" s="278"/>
+      <x:c r="D4" s="278"/>
+      <x:c r="E4" s="278"/>
+      <x:c r="F4" s="278"/>
+      <x:c r="G4" s="278"/>
+      <x:c r="H4" s="278"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="278" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="278"/>
+      <x:c r="C5" s="278"/>
+      <x:c r="D5" s="278"/>
+      <x:c r="E5" s="278"/>
+      <x:c r="F5" s="278"/>
+      <x:c r="G5" s="278"/>
+      <x:c r="H5" s="278"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="278"/>
+      <x:c r="B6" s="278"/>
+      <x:c r="C6" s="278"/>
+      <x:c r="D6" s="278"/>
+      <x:c r="E6" s="278"/>
+      <x:c r="F6" s="278"/>
+      <x:c r="G6" s="278"/>
+      <x:c r="H6" s="278"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="281" t="str">
+        <x:v>No.</x:v>
+      </x:c>
+      <x:c r="B7" s="281" t="str">
+        <x:v>ファイル名</x:v>
+      </x:c>
+      <x:c r="C7" s="281" t="str">
+        <x:v>Document ID</x:v>
+      </x:c>
+      <x:c r="D7" s="281" t="str">
+        <x:v>内容</x:v>
+      </x:c>
+      <x:c r="E7" s="281" t="str">
+        <x:v>Document Version</x:v>
+      </x:c>
+      <x:c r="F7" s="281" t="str">
+        <x:v>作成状態</x:v>
+      </x:c>
+      <x:c r="G7" s="281" t="str">
+        <x:v>レビュー</x:v>
+      </x:c>
+      <x:c r="H7" s="281" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="283" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B8" s="283" t="str">
+        <x:v>00_基本設計書総合管理.xlsx</x:v>
+      </x:c>
+      <x:c r="C8" s="283" t="str">
         <x:v>CW-BD-MGT</x:v>
       </x:c>
-      <x:c r="F3" s="160"/>
-      <x:c r="G3" s="160"/>
-      <x:c r="H3" s="160"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="200" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="160" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="160"/>
-      <x:c r="D4" s="200" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="160" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="160"/>
-      <x:c r="G4" s="160"/>
-      <x:c r="H4" s="160"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5"/>
-      <x:c r="B5"/>
-      <x:c r="C5"/>
-      <x:c r="D5"/>
-      <x:c r="E5"/>
-      <x:c r="F5"/>
-      <x:c r="G5"/>
-      <x:c r="H5"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="201" t="str">
-        <x:v>1. 文書一覧</x:v>
-      </x:c>
-      <x:c r="B6" s="201"/>
-      <x:c r="C6" s="201"/>
-      <x:c r="D6" s="201"/>
-      <x:c r="E6" s="201"/>
-      <x:c r="F6" s="201"/>
-      <x:c r="G6" s="201"/>
-      <x:c r="H6" s="201"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="207" t="str">
-        <x:v>No.</x:v>
-      </x:c>
-      <x:c r="B7" s="207" t="str">
-        <x:v>ファイル名</x:v>
-      </x:c>
-      <x:c r="C7" s="207" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D7" s="207" t="str">
-        <x:v>内容</x:v>
-      </x:c>
-      <x:c r="E7" s="207" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="F7" s="207" t="str">
-        <x:v>作成状態</x:v>
-      </x:c>
-      <x:c r="G7" s="207" t="str">
-        <x:v>レビュー</x:v>
-      </x:c>
-      <x:c r="H7" s="207" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B8" s="76" t="str">
-        <x:v>00_基本設計書総合管理.xlsx</x:v>
-      </x:c>
-      <x:c r="C8" s="76" t="str">
-        <x:v>CW-BD-MGT</x:v>
-      </x:c>
-      <x:c r="D8" s="76" t="str">
-        <x:v>基本設計書の文書管理・追跡・設計決定</x:v>
-      </x:c>
-      <x:c r="E8" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F8" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G8" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H8" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="76" t="n">
+      <x:c r="D8" s="283" t="str">
+        <x:v>基本設計書総合管理</x:v>
+      </x:c>
+      <x:c r="E8" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F8" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G8" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H8" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="282" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B9" s="76" t="str">
+      <x:c r="B9" s="282" t="str">
         <x:v>01_システム全体基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C9" s="76" t="str">
+      <x:c r="C9" s="282" t="str">
         <x:v>CW-BD-SYS</x:v>
       </x:c>
-      <x:c r="D9" s="76" t="str">
-        <x:v>システム概要・業務範囲・構成・Module</x:v>
-      </x:c>
-      <x:c r="E9" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F9" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G9" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H9" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="76" t="n">
+      <x:c r="D9" s="282" t="str">
+        <x:v>システム全体基本設計書</x:v>
+      </x:c>
+      <x:c r="E9" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F9" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G9" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H9" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="283" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B10" s="76" t="str">
+      <x:c r="B10" s="283" t="str">
         <x:v>02_権限基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C10" s="76" t="str">
+      <x:c r="C10" s="283" t="str">
         <x:v>CW-BD-AUTHZ</x:v>
       </x:c>
-      <x:c r="D10" s="76" t="str">
-        <x:v>Role・Menu・Permission・API権限対応</x:v>
-      </x:c>
-      <x:c r="E10" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F10" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G10" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H10" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="76" t="n">
+      <x:c r="D10" s="283" t="str">
+        <x:v>権限基本設計書</x:v>
+      </x:c>
+      <x:c r="E10" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F10" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G10" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H10" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="282" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B11" s="76" t="str">
+      <x:c r="B11" s="282" t="str">
         <x:v>03_画面共通設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C11" s="76" t="str">
+      <x:c r="C11" s="282" t="str">
         <x:v>CW-BD-SCR-CMN</x:v>
       </x:c>
-      <x:c r="D11" s="76" t="str">
-        <x:v>03_画面共通設計書</x:v>
-      </x:c>
-      <x:c r="E11" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F11" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G11" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H11" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="76" t="n">
+      <x:c r="D11" s="282" t="str">
+        <x:v>画面共通設計書</x:v>
+      </x:c>
+      <x:c r="E11" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F11" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G11" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H11" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="283" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B12" s="76" t="str">
+      <x:c r="B12" s="283" t="str">
         <x:v>04_認証とホーム_画面基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C12" s="76" t="str">
+      <x:c r="C12" s="283" t="str">
         <x:v>CW-BD-SCR-AUTH</x:v>
       </x:c>
-      <x:c r="D12" s="76" t="str">
-        <x:v>04_認証とホーム_画面基本設計書</x:v>
-      </x:c>
-      <x:c r="E12" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F12" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G12" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H12" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="76" t="n">
+      <x:c r="D12" s="283" t="str">
+        <x:v>認証とホーム_画面基本設計書</x:v>
+      </x:c>
+      <x:c r="E12" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F12" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G12" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H12" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="282" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B13" s="76" t="str">
+      <x:c r="B13" s="282" t="str">
         <x:v>05_従業員と部門_画面基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C13" s="76" t="str">
+      <x:c r="C13" s="282" t="str">
         <x:v>CW-BD-SCR-ORG</x:v>
       </x:c>
-      <x:c r="D13" s="76" t="str">
-        <x:v>05_従業員と部門_画面基本設計書</x:v>
-      </x:c>
-      <x:c r="E13" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F13" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G13" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H13" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="76" t="n">
+      <x:c r="D13" s="282" t="str">
+        <x:v>従業員と部門_画面基本設計書</x:v>
+      </x:c>
+      <x:c r="E13" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F13" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G13" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H13" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="283" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B14" s="76" t="str">
+      <x:c r="B14" s="283" t="str">
         <x:v>06_プロジェクト管理_画面基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C14" s="76" t="str">
+      <x:c r="C14" s="283" t="str">
         <x:v>CW-BD-SCR-PRJ</x:v>
       </x:c>
-      <x:c r="D14" s="76" t="str">
-        <x:v>06_プロジェクト管理_画面基本設計書</x:v>
-      </x:c>
-      <x:c r="E14" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F14" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G14" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H14" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="76" t="n">
+      <x:c r="D14" s="283" t="str">
+        <x:v>プロジェクト管理_画面基本設計書</x:v>
+      </x:c>
+      <x:c r="E14" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F14" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G14" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H14" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="282" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B15" s="76" t="str">
+      <x:c r="B15" s="282" t="str">
         <x:v>07_タスク管理_画面基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C15" s="76" t="str">
+      <x:c r="C15" s="282" t="str">
         <x:v>CW-BD-SCR-TSK</x:v>
       </x:c>
-      <x:c r="D15" s="76" t="str">
-        <x:v>07_タスク管理_画面基本設計書</x:v>
-      </x:c>
-      <x:c r="E15" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F15" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G15" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H15" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="76" t="n">
+      <x:c r="D15" s="282" t="str">
+        <x:v>タスク管理_画面基本設計書</x:v>
+      </x:c>
+      <x:c r="E15" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F15" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G15" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H15" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="283" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B16" s="76" t="str">
+      <x:c r="B16" s="283" t="str">
         <x:v>08_日報と通知_画面基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C16" s="76" t="str">
+      <x:c r="C16" s="283" t="str">
         <x:v>CW-BD-SCR-RPT</x:v>
       </x:c>
-      <x:c r="D16" s="76" t="str">
-        <x:v>08_日報と通知_画面基本設計書</x:v>
-      </x:c>
-      <x:c r="E16" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F16" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G16" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H16" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="76" t="n">
+      <x:c r="D16" s="283" t="str">
+        <x:v>日報と通知_画面基本設計書</x:v>
+      </x:c>
+      <x:c r="E16" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F16" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G16" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="282" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B17" s="76" t="str">
+      <x:c r="B17" s="282" t="str">
         <x:v>09_システム管理_画面基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C17" s="76" t="str">
+      <x:c r="C17" s="282" t="str">
         <x:v>CW-BD-SCR-ADM</x:v>
       </x:c>
-      <x:c r="D17" s="76" t="str">
-        <x:v>09_システム管理_画面基本設計書</x:v>
-      </x:c>
-      <x:c r="E17" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F17" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G17" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H17" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="76" t="n">
+      <x:c r="D17" s="282" t="str">
+        <x:v>システム管理_画面基本設計書</x:v>
+      </x:c>
+      <x:c r="E17" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F17" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G17" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="283" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B18" s="76" t="str">
+      <x:c r="B18" s="283" t="str">
         <x:v>10_API共通と認証_基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C18" s="76" t="str">
+      <x:c r="C18" s="283" t="str">
         <x:v>CW-BD-API-AUTH</x:v>
       </x:c>
-      <x:c r="D18" s="76" t="str">
-        <x:v>10_API共通と認証_基本設計書</x:v>
-      </x:c>
-      <x:c r="E18" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F18" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G18" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H18" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="76" t="n">
+      <x:c r="D18" s="283" t="str">
+        <x:v>API共通と認証_基本設計書</x:v>
+      </x:c>
+      <x:c r="E18" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F18" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G18" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="282" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B19" s="76" t="str">
+      <x:c r="B19" s="282" t="str">
         <x:v>11_従業員と部門_API基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C19" s="76" t="str">
+      <x:c r="C19" s="282" t="str">
         <x:v>CW-BD-API-ORG</x:v>
       </x:c>
-      <x:c r="D19" s="76" t="str">
-        <x:v>11_従業員と部門_API基本設計書</x:v>
-      </x:c>
-      <x:c r="E19" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F19" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G19" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H19" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="76" t="n">
+      <x:c r="D19" s="282" t="str">
+        <x:v>従業員と部門_API基本設計書</x:v>
+      </x:c>
+      <x:c r="E19" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F19" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G19" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="283" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B20" s="76" t="str">
+      <x:c r="B20" s="283" t="str">
         <x:v>12_プロジェクト_API基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C20" s="76" t="str">
+      <x:c r="C20" s="283" t="str">
         <x:v>CW-BD-API-PRJ</x:v>
       </x:c>
-      <x:c r="D20" s="76" t="str">
-        <x:v>12_プロジェクト_API基本設計書</x:v>
-      </x:c>
-      <x:c r="E20" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F20" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G20" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H20" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="76" t="n">
+      <x:c r="D20" s="283" t="str">
+        <x:v>プロジェクト_API基本設計書</x:v>
+      </x:c>
+      <x:c r="E20" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F20" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G20" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H20" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="282" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B21" s="76" t="str">
+      <x:c r="B21" s="282" t="str">
         <x:v>13_タスクとファイル_API基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C21" s="76" t="str">
+      <x:c r="C21" s="282" t="str">
         <x:v>CW-BD-API-TSK</x:v>
       </x:c>
-      <x:c r="D21" s="76" t="str">
-        <x:v>13_タスクとファイル_API基本設計書</x:v>
-      </x:c>
-      <x:c r="E21" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F21" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G21" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H21" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="76" t="n">
+      <x:c r="D21" s="282" t="str">
+        <x:v>タスクとファイル_API基本設計書</x:v>
+      </x:c>
+      <x:c r="E21" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F21" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G21" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H21" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="283" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B22" s="76" t="str">
+      <x:c r="B22" s="283" t="str">
         <x:v>14_日報と通知_API基本設計書.xlsx</x:v>
       </x:c>
-      <x:c r="C22" s="76" t="str">
+      <x:c r="C22" s="283" t="str">
         <x:v>CW-BD-API-RPT</x:v>
       </x:c>
-      <x:c r="D22" s="76" t="str">
-        <x:v>14_日報と通知_API基本設計書</x:v>
-      </x:c>
-      <x:c r="E22" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F22" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G22" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H22" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="76" t="n">
+      <x:c r="D22" s="283" t="str">
+        <x:v>日報と通知_API基本設計書</x:v>
+      </x:c>
+      <x:c r="E22" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F22" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G22" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H22" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="282" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B23" s="76" t="str">
-        <x:v>15_ユーザーと組織_DB基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C23" s="76" t="str">
-        <x:v>CW-BD-DB-ORG</x:v>
-      </x:c>
-      <x:c r="D23" s="76" t="str">
-        <x:v>15_ユーザーと組織_DB基本設計書</x:v>
-      </x:c>
-      <x:c r="E23" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F23" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G23" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H23" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="76" t="n">
+      <x:c r="B23" s="282" t="str">
+        <x:v>15_DB基本設計書.xlsx</x:v>
+      </x:c>
+      <x:c r="C23" s="282" t="str">
+        <x:v>CW-BD-DB</x:v>
+      </x:c>
+      <x:c r="D23" s="282" t="str">
+        <x:v>DB基本設計書</x:v>
+      </x:c>
+      <x:c r="E23" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F23" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G23" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H23" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I23"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="283" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B24" s="76" t="str">
-        <x:v>16_プロジェクトとタスク_DB基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C24" s="76" t="str">
-        <x:v>CW-BD-DB-TSK</x:v>
-      </x:c>
-      <x:c r="D24" s="76" t="str">
-        <x:v>16_プロジェクトとタスク_DB基本設計書</x:v>
-      </x:c>
-      <x:c r="E24" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F24" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G24" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H24" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="76" t="n">
+      <x:c r="B24" s="283" t="str">
+        <x:v>16_業務ルールと状態遷移_基本設計書.xlsx</x:v>
+      </x:c>
+      <x:c r="C24" s="283" t="str">
+        <x:v>CW-BD-BIZ</x:v>
+      </x:c>
+      <x:c r="D24" s="283" t="str">
+        <x:v>業務ルールと状態遷移_基本設計書</x:v>
+      </x:c>
+      <x:c r="E24" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F24" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G24" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H24" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I24"/>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="282" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B25" s="76" t="str">
-        <x:v>17_日報通知ログ_DB基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C25" s="76" t="str">
-        <x:v>CW-BD-DB-RPT</x:v>
-      </x:c>
-      <x:c r="D25" s="76" t="str">
-        <x:v>17_日報通知ログ_DB基本設計書</x:v>
-      </x:c>
-      <x:c r="E25" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F25" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G25" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H25" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="76" t="n">
+      <x:c r="B25" s="282" t="str">
+        <x:v>17_トランザクションと排他_基本設計書.xlsx</x:v>
+      </x:c>
+      <x:c r="C25" s="282" t="str">
+        <x:v>CW-BD-TX</x:v>
+      </x:c>
+      <x:c r="D25" s="282" t="str">
+        <x:v>トランザクションと排他_基本設計書</x:v>
+      </x:c>
+      <x:c r="E25" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F25" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G25" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H25" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I25"/>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="283" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B26" s="76" t="str">
-        <x:v>18_業務ルールと状態遷移_基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C26" s="76" t="str">
-        <x:v>CW-BD-BIZ</x:v>
-      </x:c>
-      <x:c r="D26" s="76" t="str">
-        <x:v>18_業務ルールと状態遷移_基本設計書</x:v>
-      </x:c>
-      <x:c r="E26" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F26" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G26" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H26" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="76" t="n">
+      <x:c r="B26" s="283" t="str">
+        <x:v>18_メッセージと例外_基本設計書.xlsx</x:v>
+      </x:c>
+      <x:c r="C26" s="283" t="str">
+        <x:v>CW-BD-EX</x:v>
+      </x:c>
+      <x:c r="D26" s="283" t="str">
+        <x:v>メッセージと例外_基本設計書</x:v>
+      </x:c>
+      <x:c r="E26" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F26" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G26" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H26" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I26"/>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
+    </x:row>
+    <x:row r="27" ht="57" customHeight="1">
+      <x:c r="A27" s="282" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B27" s="76" t="str">
-        <x:v>19_トランザクションと排他_基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C27" s="76" t="str">
-        <x:v>CW-BD-TX</x:v>
-      </x:c>
-      <x:c r="D27" s="76" t="str">
-        <x:v>19_トランザクションと排他_基本設計書</x:v>
-      </x:c>
-      <x:c r="E27" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F27" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G27" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H27" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="30" customHeight="1">
-      <x:c r="A28" s="76" t="n">
+      <x:c r="B27" s="282" t="str">
+        <x:v>19_ログファイルRedisセキュリティ_基本設計書.xlsx</x:v>
+      </x:c>
+      <x:c r="C27" s="282" t="str">
+        <x:v>CW-BD-CMN</x:v>
+      </x:c>
+      <x:c r="D27" s="282" t="str">
+        <x:v>ログファイルRedisセキュリティ_基本設計書</x:v>
+      </x:c>
+      <x:c r="E27" s="282" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F27" s="282" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G27" s="282" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H27" s="282" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I27"/>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="283" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B28" s="76" t="str">
-        <x:v>20_メッセージと例外_基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C28" s="76" t="str">
-        <x:v>CW-BD-EX</x:v>
-      </x:c>
-      <x:c r="D28" s="76" t="str">
-        <x:v>20_メッセージと例外_基本設計書</x:v>
-      </x:c>
-      <x:c r="E28" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F28" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G28" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H28" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="76" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B29" s="76" t="str">
-        <x:v>21_ログファイルRedisセキュリティ_基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C29" s="76" t="str">
-        <x:v>CW-BD-CMN</x:v>
-      </x:c>
-      <x:c r="D29" s="76" t="str">
-        <x:v>21_ログファイルRedisセキュリティ_基本設計書</x:v>
-      </x:c>
-      <x:c r="E29" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F29" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G29" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H29" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="76" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B30" s="76" t="str">
-        <x:v>22_バッチ非機能運用_基本設計書.xlsx</x:v>
-      </x:c>
-      <x:c r="C30" s="76" t="str">
+      <x:c r="B28" s="283" t="str">
+        <x:v>20_バッチ非機能運用_基本設計書.xlsx</x:v>
+      </x:c>
+      <x:c r="C28" s="283" t="str">
         <x:v>CW-BD-OPS</x:v>
       </x:c>
-      <x:c r="D30" s="76" t="str">
-        <x:v>22_バッチ非機能運用_基本設計書</x:v>
-      </x:c>
-      <x:c r="E30" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F30" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G30" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H30" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="76" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B31" s="76" t="str">
-        <x:v>23_学員Reviewテスト管理.xlsx</x:v>
-      </x:c>
-      <x:c r="C31" s="76" t="str">
-        <x:v>CW-BD-U-MGT</x:v>
-      </x:c>
-      <x:c r="D31" s="76" t="str">
-        <x:v>23_学員Reviewテスト管理</x:v>
-      </x:c>
-      <x:c r="E31" s="76" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="F31" s="76" t="str">
-        <x:v>完了</x:v>
-      </x:c>
-      <x:c r="G31" s="76" t="str">
-        <x:v>レビュー待ち</x:v>
-      </x:c>
-      <x:c r="H31" s="76" t="str">
-        <x:v>Ver.1.8 再監査第2回反映</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="212" t="str">
-        <x:v>24本文書をVer.1.8の単一Baselineとして管理する。</x:v>
-      </x:c>
-      <x:c r="B33" s="212"/>
-      <x:c r="C33" s="212"/>
-      <x:c r="D33" s="212"/>
-      <x:c r="E33" s="212"/>
-      <x:c r="F33" s="212"/>
-      <x:c r="G33" s="212"/>
-      <x:c r="H33" s="212"/>
+      <x:c r="D28" s="283" t="str">
+        <x:v>バッチ非機能運用_基本設計書</x:v>
+      </x:c>
+      <x:c r="E28" s="283" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="F28" s="283" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="G28" s="283" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H28" s="283" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="I28"/>
+      <x:c r="J28"/>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
+    </x:row>
+    <x:row r="29" ht="40" customHeight="1">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
+    </x:row>
+    <x:row r="30" ht="40" customHeight="1">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+      <x:c r="I30"/>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
+    </x:row>
+    <x:row r="31" ht="40" customHeight="1">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+      <x:c r="I31"/>
+      <x:c r="J31"/>
+      <x:c r="K31"/>
+      <x:c r="L31"/>
+    </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+      <x:c r="I33"/>
+      <x:c r="J33"/>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="212"/>
-      <x:c r="B34" s="212"/>
-      <x:c r="C34" s="212"/>
-      <x:c r="D34" s="212"/>
-      <x:c r="E34" s="212"/>
-      <x:c r="F34" s="212"/>
-      <x:c r="G34" s="212"/>
-      <x:c r="H34" s="212"/>
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A6:H6"/>
-    <x:mergeCell ref="A33:H34"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3423,8 +4441,8 @@
       <x:c r="C3" s="160"/>
       <x:c r="D3" s="160"/>
       <x:c r="E3" s="160"/>
-      <x:c r="F3" s="200" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="F3" s="275" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="G3" s="160" t="str">
         <x:v>CW-BD-005</x:v>
@@ -3439,8 +4457,8 @@
       <x:c r="A4" s="200" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="160" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="72" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="160"/>
       <x:c r="D4" s="160"/>
@@ -3448,8 +4466,8 @@
       <x:c r="F4" s="200" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="G4" s="160" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="G4" s="72" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="160"/>
       <x:c r="I4" s="160"/>
@@ -3467,6 +4485,9 @@
       <x:c r="G5"/>
       <x:c r="H5"/>
       <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="201" t="str">
@@ -3513,7 +4534,7 @@
         <x:v>Error Code</x:v>
       </x:c>
       <x:c r="J7" s="207" t="str">
-        <x:v>Message ID</x:v>
+        <x:v>主要Message ID</x:v>
       </x:c>
       <x:c r="K7" s="207" t="str">
         <x:v>詳細設計成果物</x:v>
@@ -3548,10 +4569,10 @@
         <x:v>TX-011</x:v>
       </x:c>
       <x:c r="I8" s="76" t="str">
-        <x:v>AUTH-4001, AUTH-4004, AUTH-4005,COMMON-5000</x:v>
+        <x:v>AUTH-4001, AUTH-4004, AUTH-4005, COMMON-5000, AUTH-4290</x:v>
       </x:c>
       <x:c r="J8" s="76" t="str">
-        <x:v>-</x:v>
+        <x:v>MSG-E-008</x:v>
       </x:c>
       <x:c r="K8" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -3586,7 +4607,7 @@
         <x:v>TX-012</x:v>
       </x:c>
       <x:c r="I9" s="76" t="str">
-        <x:v>AUTH-4002,COMMON-5000</x:v>
+        <x:v>AUTH-4002, COMMON-5000</x:v>
       </x:c>
       <x:c r="J9" s="76" t="str">
         <x:v>MSG-C-003</x:v>
@@ -3700,7 +4721,7 @@
         <x:v>TX-014</x:v>
       </x:c>
       <x:c r="I12" s="76" t="str">
-        <x:v>AUTH-4001, AUTH-4002,COMMON-4000</x:v>
+        <x:v>AUTH-4001, AUTH-4002, COMMON-4000</x:v>
       </x:c>
       <x:c r="J12" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-005</x:v>
@@ -3729,10 +4750,10 @@
         <x:v>PERM-DASH-READ</x:v>
       </x:c>
       <x:c r="F13" s="76" t="str">
-        <x:v>projects,tasks,daily_reports,notifications</x:v>
+        <x:v>projects,project_members,tasks,daily_reports,notifications</x:v>
       </x:c>
       <x:c r="G13" s="76" t="str">
-        <x:v>-</x:v>
+        <x:v>BR-DASH-001</x:v>
       </x:c>
       <x:c r="H13" s="76" t="str">
         <x:v>-</x:v>
@@ -3846,16 +4867,16 @@
         <x:v>departments,operation_logs / Redis</x:v>
       </x:c>
       <x:c r="G16" s="76" t="str">
-        <x:v>BR-DEPT-001, BR-DEPT-002, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
+        <x:v>BR-DEPT-003, BR-DEPT-005, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H16" s="76" t="str">
         <x:v>TX-017</x:v>
       </x:c>
       <x:c r="I16" s="76" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4000, COMMON-4090</x:v>
+        <x:v>DEPT-4001, COMMON-4000, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J16" s="76" t="str">
-        <x:v>MSG-C-001, MSG-I-001</x:v>
+        <x:v>MSG-C-001, MSG-I-012</x:v>
       </x:c>
       <x:c r="K16" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -3881,19 +4902,19 @@
         <x:v>PERM-DEPT-WRITE</x:v>
       </x:c>
       <x:c r="F17" s="76" t="str">
-        <x:v>departments,operation_logs / Redis</x:v>
+        <x:v>departments,employees,operation_logs / Redis</x:v>
       </x:c>
       <x:c r="G17" s="76" t="str">
-        <x:v>BR-DEPT-001, BR-DEPT-002, BR-DATA-001, BR-LOG-001</x:v>
+        <x:v>BR-DEPT-001, BR-DEPT-003, BR-DEPT-004, BR-DEPT-005, BR-DATA-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H17" s="76" t="str">
         <x:v>TX-017</x:v>
       </x:c>
       <x:c r="I17" s="76" t="str">
-        <x:v>DEPT-4001, DEPT-4002,COMMON-4040, COMMON-4090</x:v>
+        <x:v>DEPT-4001, DEPT-4002, DEPT-4003, DEPT-4004, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J17" s="76" t="str">
-        <x:v>MSG-C-001, MSG-I-003</x:v>
+        <x:v>MSG-C-001, MSG-C-007, MSG-I-013, MSG-I-014, MSG-E-015, MSG-E-016</x:v>
       </x:c>
       <x:c r="K17" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -3919,19 +4940,19 @@
         <x:v>PERM-DEPT-WRITE</x:v>
       </x:c>
       <x:c r="F18" s="76" t="str">
-        <x:v>departments,employees,projects / Redis</x:v>
+        <x:v>departments,employees,operation_logs / Redis</x:v>
       </x:c>
       <x:c r="G18" s="76" t="str">
-        <x:v>BR-DEPT-001, BR-DEPT-002, BR-DATA-001, BR-LOG-001</x:v>
+        <x:v>BR-DEPT-002, BR-DEPT-005, BR-DATA-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H18" s="76" t="str">
         <x:v>TX-017</x:v>
       </x:c>
       <x:c r="I18" s="76" t="str">
-        <x:v>DEPT-4002, DEPT-4003,COMMON-4090</x:v>
+        <x:v>DEPT-4002, DEPT-4003, DEPT-4004, COMMON-4090</x:v>
       </x:c>
       <x:c r="J18" s="76" t="str">
-        <x:v>MSG-C-002, MSG-I-002</x:v>
+        <x:v>MSG-C-002, MSG-I-002, MSG-E-012, MSG-E-013, MSG-E-014, MSG-E-015</x:v>
       </x:c>
       <x:c r="K18" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -3960,7 +4981,7 @@
         <x:v>employees,departments,users,project_members</x:v>
       </x:c>
       <x:c r="G19" s="76" t="str">
-        <x:v>-</x:v>
+        <x:v>BR-EMP-005</x:v>
       </x:c>
       <x:c r="H19" s="76" t="str">
         <x:v>-</x:v>
@@ -3998,13 +5019,13 @@
         <x:v>employees,departments,projects,tasks</x:v>
       </x:c>
       <x:c r="G20" s="76" t="str">
-        <x:v>-</x:v>
+        <x:v>BR-EMP-005</x:v>
       </x:c>
       <x:c r="H20" s="76" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I20" s="76" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
+        <x:v>COMMON-4040, AUTH-4006</x:v>
       </x:c>
       <x:c r="J20" s="76" t="str">
         <x:v>-</x:v>
@@ -4036,16 +5057,16 @@
         <x:v>employees,users,user_roles,operation_logs</x:v>
       </x:c>
       <x:c r="G21" s="76" t="str">
-        <x:v>BR-EMP-001, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
+        <x:v>BR-EMP-001, BR-EMP-004, BR-EMP-006, BR-EMP-008, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H21" s="76" t="str">
         <x:v>TX-001</x:v>
       </x:c>
       <x:c r="I21" s="76" t="str">
-        <x:v>EMP-4001, EMP-4002, EMP-4003,COMMON-4000, COMMON-4090</x:v>
+        <x:v>EMP-4001, EMP-4002, EMP-4003, EMP-4006, COMMON-4000, COMMON-4090</x:v>
       </x:c>
       <x:c r="J21" s="76" t="str">
-        <x:v>MSG-C-001, MSG-I-001</x:v>
+        <x:v>MSG-C-001, MSG-I-007, MSG-E-009, MSG-E-018</x:v>
       </x:c>
       <x:c r="K21" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -4074,16 +5095,16 @@
         <x:v>employees,operation_logs</x:v>
       </x:c>
       <x:c r="G22" s="76" t="str">
-        <x:v>BR-EMP-001, BR-DATA-001, BR-LOG-001</x:v>
+        <x:v>BR-EMP-001, BR-EMP-006, BR-DATA-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H22" s="76" t="str">
         <x:v>TX-015</x:v>
       </x:c>
       <x:c r="I22" s="76" t="str">
-        <x:v>EMP-4002,COMMON-4040, COMMON-4090</x:v>
+        <x:v>EMP-4002, EMP-4006, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J22" s="76" t="str">
-        <x:v>MSG-C-001, MSG-I-003</x:v>
+        <x:v>MSG-C-001, MSG-I-008, MSG-E-009, MSG-E-015</x:v>
       </x:c>
       <x:c r="K22" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -4097,7 +5118,7 @@
         <x:v>M03</x:v>
       </x:c>
       <x:c r="B23" s="76" t="str">
-        <x:v>SCR-005, SCR-006</x:v>
+        <x:v>SCR-005</x:v>
       </x:c>
       <x:c r="C23" s="76" t="str">
         <x:v>従業員状態変更</x:v>
@@ -4109,19 +5130,19 @@
         <x:v>PERM-EMP-WRITE</x:v>
       </x:c>
       <x:c r="F23" s="76" t="str">
-        <x:v>employees,users,tasks,refresh_tokens / Redis</x:v>
+        <x:v>employees,users,tasks,project_members,refresh_tokens,operation_logs / Redis</x:v>
       </x:c>
       <x:c r="G23" s="76" t="str">
-        <x:v>BR-EMP-002, BR-EMP-003, BR-DATA-001, BR-LOG-001</x:v>
+        <x:v>BR-EMP-003, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H23" s="76" t="str">
         <x:v>TX-005</x:v>
       </x:c>
       <x:c r="I23" s="76" t="str">
-        <x:v>EMP-4004,COMMON-4040, COMMON-4090</x:v>
+        <x:v>EMP-4005, EMP-4006, EMP-4007, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J23" s="76" t="str">
-        <x:v>MSG-C-004, MSG-I-003</x:v>
+        <x:v>MSG-C-006, MSG-I-009, MSG-E-010, MSG-E-011, MSG-E-015</x:v>
       </x:c>
       <x:c r="K23" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -4150,16 +5171,16 @@
         <x:v>employees,users,user_roles,operation_logs</x:v>
       </x:c>
       <x:c r="G24" s="76" t="str">
-        <x:v>BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
+        <x:v>BR-EMP-001, BR-EMP-004, BR-EMP-006, BR-EMP-007, BR-EMP-008, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H24" s="76" t="str">
         <x:v>TX-016</x:v>
       </x:c>
       <x:c r="I24" s="76" t="str">
-        <x:v>FILE-4001, FILE-4002,EMP-4001, EMP-4002, EMP-4003</x:v>
+        <x:v>FILE-4001, FILE-4002, EMP-4001, EMP-4002, EMP-4003, EMP-4006, COMMON-4000</x:v>
       </x:c>
       <x:c r="J24" s="76" t="str">
-        <x:v>MSG-C-001, MSG-I-001</x:v>
+        <x:v>MSG-C-008, MSG-I-010, MSG-E-009, MSG-E-017, MSG-E-018</x:v>
       </x:c>
       <x:c r="K24" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -4197,7 +5218,7 @@
         <x:v>COMMON-4000</x:v>
       </x:c>
       <x:c r="J25" s="76" t="str">
-        <x:v>-</x:v>
+        <x:v>MSG-I-011</x:v>
       </x:c>
       <x:c r="K25" s="76" t="str">
         <x:v>画面詳細設計 + API詳細設計</x:v>
@@ -4284,7 +5305,7 @@
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
       <x:c r="A28" s="76" t="str">
-        <x:v>M00</x:v>
+        <x:v>COMMON</x:v>
       </x:c>
       <x:c r="B28" s="76" t="str">
         <x:v>SCR-003, SCR-004, SCR-007, SCR-021</x:v>
@@ -4322,7 +5343,7 @@
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
       <x:c r="A29" s="76" t="str">
-        <x:v>M00</x:v>
+        <x:v>COMMON</x:v>
       </x:c>
       <x:c r="B29" s="76" t="str">
         <x:v>SCR-007, SCR-009, SCR-012, SCR-013, SCR-015, SCR-021</x:v>
@@ -4334,7 +5355,7 @@
         <x:v>API-MST-002</x:v>
       </x:c>
       <x:c r="E29" s="76" t="str">
-        <x:v>PERM-EMP-READ</x:v>
+        <x:v>02／13_API権限対応 API-MST-002（context別Permission）</x:v>
       </x:c>
       <x:c r="F29" s="76" t="str">
         <x:v>employees,project_members</x:v>
@@ -4346,7 +5367,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I29" s="76" t="str">
-        <x:v>AUTH-4006</x:v>
+        <x:v>COMMON-4000, AUTH-4006</x:v>
       </x:c>
       <x:c r="J29" s="76" t="str">
         <x:v>-</x:v>
@@ -4360,7 +5381,7 @@
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
       <x:c r="A30" s="76" t="str">
-        <x:v>M00</x:v>
+        <x:v>COMMON</x:v>
       </x:c>
       <x:c r="B30" s="76" t="str">
         <x:v>SCR-013, SCR-015, SCR-018, SCR-019, SCR-020, SCR-021</x:v>
@@ -4398,7 +5419,7 @@
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
       <x:c r="A31" s="76" t="str">
-        <x:v>M00</x:v>
+        <x:v>COMMON</x:v>
       </x:c>
       <x:c r="B31" s="76" t="str">
         <x:v>SCR-004, SCR-023, SCR-024</x:v>
@@ -4477,7 +5498,7 @@
         <x:v>M08</x:v>
       </x:c>
       <x:c r="B33" s="76" t="str">
-        <x:v>共通Header/SCR-002</x:v>
+        <x:v>共通Header</x:v>
       </x:c>
       <x:c r="C33" s="76" t="str">
         <x:v>未読件数</x:v>
@@ -4536,7 +5557,7 @@
         <x:v>TX-024</x:v>
       </x:c>
       <x:c r="I34" s="76" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
+        <x:v>COMMON-4040, AUTH-4006</x:v>
       </x:c>
       <x:c r="J34" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-003</x:v>
@@ -4548,7 +5569,7 @@
         <x:v>UT-NTF-003 / IT-NTF-003</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
+    <x:row r="35" ht="105" customHeight="1">
       <x:c r="A35" s="76" t="str">
         <x:v>M08</x:v>
       </x:c>
@@ -4568,7 +5589,7 @@
         <x:v>notifications</x:v>
       </x:c>
       <x:c r="G35" s="76" t="str">
-        <x:v>BR-NTF-001, BR-DATA-001, BR-LOG-001</x:v>
+        <x:v>BR-NTF-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H35" s="76" t="str">
         <x:v>TX-024</x:v>
@@ -4586,7 +5607,7 @@
         <x:v>UT-NTF-004 / IT-NTF-004</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
+    <x:row r="36" ht="105" customHeight="1">
       <x:c r="A36" s="76" t="str">
         <x:v>M05</x:v>
       </x:c>
@@ -4650,7 +5671,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I37" s="76" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
+        <x:v>COMMON-4040, AUTH-4006</x:v>
       </x:c>
       <x:c r="J37" s="76" t="str">
         <x:v>-</x:v>
@@ -4688,7 +5709,7 @@
         <x:v>TX-002</x:v>
       </x:c>
       <x:c r="I38" s="76" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4090</x:v>
+        <x:v>COMMON-4000, PRJ-4001, PRJ-4002, COMMON-4090</x:v>
       </x:c>
       <x:c r="J38" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-001</x:v>
@@ -4726,7 +5747,7 @@
         <x:v>TX-003</x:v>
       </x:c>
       <x:c r="I39" s="76" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4040, COMMON-4090</x:v>
+        <x:v>COMMON-4000, PRJ-4002, PRJ-4003, PRJ-4004, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J39" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-003</x:v>
@@ -4764,7 +5785,7 @@
         <x:v>TX-018</x:v>
       </x:c>
       <x:c r="I40" s="76" t="str">
-        <x:v>PRJ-4003,COMMON-4090</x:v>
+        <x:v>PRJ-4003, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J40" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-003</x:v>
@@ -4840,7 +5861,7 @@
         <x:v>TX-019</x:v>
       </x:c>
       <x:c r="I42" s="76" t="str">
-        <x:v>PRJ-4004,COMMON-4090</x:v>
+        <x:v>COMMON-4000, PRJ-4003, PRJ-4004, COMMON-4090</x:v>
       </x:c>
       <x:c r="J42" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-001</x:v>
@@ -4872,13 +5893,13 @@
         <x:v>project_members,tasks,operation_logs</x:v>
       </x:c>
       <x:c r="G43" s="76" t="str">
-        <x:v>BR-MEM-001, BR-MEM-002, BR-DATA-001, BR-LOG-001</x:v>
+        <x:v>BR-MEM-002, BR-DATA-001, BR-LOG-001</x:v>
       </x:c>
       <x:c r="H43" s="76" t="str">
         <x:v>TX-019</x:v>
       </x:c>
       <x:c r="I43" s="76" t="str">
-        <x:v>PRJ-4005,COMMON-4090</x:v>
+        <x:v>PRJ-4003, PRJ-4005, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J43" s="76" t="str">
         <x:v>MSG-C-002, MSG-I-002</x:v>
@@ -5068,7 +6089,7 @@
         <x:v>TX-008</x:v>
       </x:c>
       <x:c r="I48" s="76" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
+        <x:v>COMMON-4000, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J48" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-003</x:v>
@@ -5106,7 +6127,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I49" s="76" t="str">
-        <x:v>COMMON-4000/AUTH-4006</x:v>
+        <x:v>COMMON-4000, AUTH-4006</x:v>
       </x:c>
       <x:c r="J49" s="76" t="str">
         <x:v>-</x:v>
@@ -5144,7 +6165,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I50" s="76" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
+        <x:v>COMMON-4040, AUTH-4006</x:v>
       </x:c>
       <x:c r="J50" s="76" t="str">
         <x:v>-</x:v>
@@ -5176,13 +6197,13 @@
         <x:v>daily_reports,daily_report_tasks,operation_logs</x:v>
       </x:c>
       <x:c r="G51" s="76" t="str">
-        <x:v>BR-RPT-001, BR-RPT-002, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
+        <x:v>BR-RPT-001, BR-RPT-002, BR-DATA-001, BR-API-001, BR-LOG-001, BR-RPT-003</x:v>
       </x:c>
       <x:c r="H51" s="76" t="str">
         <x:v>TX-006</x:v>
       </x:c>
       <x:c r="I51" s="76" t="str">
-        <x:v>RPT-4001, RPT-4002,COMMON-4090</x:v>
+        <x:v>RPT-4001, RPT-4002, COMMON-4090, RPT-4003, COMMON-4000</x:v>
       </x:c>
       <x:c r="J51" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-001</x:v>
@@ -5214,13 +6235,13 @@
         <x:v>daily_reports,daily_report_tasks,operation_logs</x:v>
       </x:c>
       <x:c r="G52" s="76" t="str">
-        <x:v>BR-RPT-001, BR-RPT-002, BR-DATA-001, BR-LOG-001</x:v>
+        <x:v>BR-RPT-001, BR-RPT-002, BR-DATA-001, BR-LOG-001, BR-RPT-003</x:v>
       </x:c>
       <x:c r="H52" s="76" t="str">
         <x:v>TX-023</x:v>
       </x:c>
       <x:c r="I52" s="76" t="str">
-        <x:v>RPT-4002,COMMON-4040, COMMON-4090</x:v>
+        <x:v>RPT-4002, COMMON-4040, COMMON-4090, RPT-4003, COMMON-4000</x:v>
       </x:c>
       <x:c r="J52" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-003</x:v>
@@ -5258,7 +6279,7 @@
         <x:v>TX-023</x:v>
       </x:c>
       <x:c r="I53" s="76" t="str">
-        <x:v>RPT-4002,COMMON-4090</x:v>
+        <x:v>RPT-4002, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J53" s="76" t="str">
         <x:v>MSG-C-002, MSG-I-002</x:v>
@@ -5270,7 +6291,7 @@
         <x:v>UT-RPT-005 / IT-RPT-005</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
+    <x:row r="54" ht="40" customHeight="1">
       <x:c r="A54" s="76" t="str">
         <x:v>M07</x:v>
       </x:c>
@@ -5290,13 +6311,13 @@
         <x:v>employees,project_members,daily_reports,business_holidays</x:v>
       </x:c>
       <x:c r="G54" s="76" t="str">
-        <x:v>-</x:v>
+        <x:v>BR-RPT-005</x:v>
       </x:c>
       <x:c r="H54" s="76" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I54" s="76" t="str">
-        <x:v>COMMON-4000</x:v>
+        <x:v>COMMON-4000, AUTH-4006</x:v>
       </x:c>
       <x:c r="J54" s="76" t="str">
         <x:v>-</x:v>
@@ -5372,7 +6393,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I56" s="76" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
+        <x:v>COMMON-4040, AUTH-4006</x:v>
       </x:c>
       <x:c r="J56" s="76" t="str">
         <x:v>-</x:v>
@@ -5410,7 +6431,7 @@
         <x:v>TX-020</x:v>
       </x:c>
       <x:c r="I57" s="76" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
+        <x:v>TASK-4002, TASK-4003, COMMON-4090, TASK-4001</x:v>
       </x:c>
       <x:c r="J57" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-001</x:v>
@@ -5448,7 +6469,7 @@
         <x:v>TX-021</x:v>
       </x:c>
       <x:c r="I58" s="76" t="str">
-        <x:v>TASK-4002, TASK-4003,COMMON-4090</x:v>
+        <x:v>TASK-4002, TASK-4003, COMMON-4090, TASK-4001</x:v>
       </x:c>
       <x:c r="J58" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-003</x:v>
@@ -5486,7 +6507,7 @@
         <x:v>TX-004</x:v>
       </x:c>
       <x:c r="I59" s="76" t="str">
-        <x:v>TASK-4001,COMMON-4090</x:v>
+        <x:v>TASK-4001, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J59" s="76" t="str">
         <x:v>MSG-C-005, MSG-I-006</x:v>
@@ -5524,7 +6545,7 @@
         <x:v>TX-021</x:v>
       </x:c>
       <x:c r="I60" s="76" t="str">
-        <x:v>COMMON-4000, COMMON-4090</x:v>
+        <x:v>COMMON-4000, TASK-4001, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="J60" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-003</x:v>
@@ -5562,7 +6583,7 @@
         <x:v>TX-022</x:v>
       </x:c>
       <x:c r="I61" s="76" t="str">
-        <x:v>COMMON-4000, COMMON-4040</x:v>
+        <x:v>COMMON-4000, COMMON-4040, TASK-4001</x:v>
       </x:c>
       <x:c r="J61" s="76" t="str">
         <x:v>MSG-C-001, MSG-I-001</x:v>
@@ -5638,7 +6659,7 @@
         <x:v>TX-007</x:v>
       </x:c>
       <x:c r="I63" s="76" t="str">
-        <x:v>FILE-4001, FILE-4002,COMMON-4090</x:v>
+        <x:v>FILE-4001, FILE-4002, COMMON-4090, TASK-4001</x:v>
       </x:c>
       <x:c r="J63" s="76" t="str">
         <x:v>MSG-I-004</x:v>
@@ -5676,7 +6697,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I64" s="76" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
+        <x:v>COMMON-4040, AUTH-4006</x:v>
       </x:c>
       <x:c r="J64" s="76" t="str">
         <x:v>-</x:v>
@@ -5714,7 +6735,7 @@
         <x:v>TX-009</x:v>
       </x:c>
       <x:c r="I65" s="76" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
+        <x:v>COMMON-4040, COMMON-4090, TASK-4001</x:v>
       </x:c>
       <x:c r="J65" s="76" t="str">
         <x:v>MSG-C-002, MSG-I-002</x:v>
@@ -5878,45 +6899,267 @@
         <x:v>UT-USR-004 / IT-USR-004</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="212" t="str">
-        <x:v>M01～M12を本教育Projectの機能要件Baselineとする。Error/Message/Rule/Transaction IDは省略せず完全記載する。</x:v>
-      </x:c>
-      <x:c r="B71" s="212"/>
-      <x:c r="C71" s="212"/>
-      <x:c r="D71" s="212"/>
-      <x:c r="E71" s="212"/>
-      <x:c r="F71" s="212"/>
-      <x:c r="G71" s="212"/>
-      <x:c r="H71" s="212"/>
-      <x:c r="I71" s="212"/>
-      <x:c r="J71" s="212"/>
-      <x:c r="K71" s="212"/>
-      <x:c r="L71" s="212"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="212"/>
-      <x:c r="B72" s="212"/>
-      <x:c r="C72" s="212"/>
-      <x:c r="D72" s="212"/>
-      <x:c r="E72" s="212"/>
-      <x:c r="F72" s="212"/>
-      <x:c r="G72" s="212"/>
-      <x:c r="H72" s="212"/>
-      <x:c r="I72" s="212"/>
-      <x:c r="J72" s="212"/>
-      <x:c r="K72" s="212"/>
-      <x:c r="L72" s="212"/>
+    <x:row r="70">
+      <x:c r="A70"/>
+      <x:c r="B70"/>
+      <x:c r="C70"/>
+      <x:c r="D70"/>
+      <x:c r="E70"/>
+      <x:c r="F70"/>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
+      <x:c r="J70"/>
+      <x:c r="K70"/>
+      <x:c r="L70"/>
+    </x:row>
+    <x:row r="71" ht="38" customHeight="1">
+      <x:c r="A71" s="267" t="str">
+        <x:v>M01～M12を機能要件Baselineとする。Error Code / Rule / Transaction IDを記載する。Message Mappingは18_メッセージと例外を正本とする。主要Message IDの「-」は本表では重複管理しないことを示す。参照APIのTransactionは「-」。COMMONは共通処理であり機能Module数に含めない。</x:v>
+      </x:c>
+      <x:c r="B71" s="267"/>
+      <x:c r="C71" s="267"/>
+      <x:c r="D71" s="267"/>
+      <x:c r="E71" s="267"/>
+      <x:c r="F71" s="267"/>
+      <x:c r="G71" s="267"/>
+      <x:c r="H71" s="267"/>
+      <x:c r="I71" s="267"/>
+      <x:c r="J71" s="267"/>
+      <x:c r="K71" s="267"/>
+      <x:c r="L71" s="267"/>
+    </x:row>
+    <x:row r="72" ht="38" customHeight="1">
+      <x:c r="A72" s="267"/>
+      <x:c r="B72" s="267"/>
+      <x:c r="C72" s="267"/>
+      <x:c r="D72" s="267"/>
+      <x:c r="E72" s="267"/>
+      <x:c r="F72" s="267"/>
+      <x:c r="G72" s="267"/>
+      <x:c r="H72" s="267"/>
+      <x:c r="I72" s="267"/>
+      <x:c r="J72" s="267"/>
+      <x:c r="K72" s="267"/>
+      <x:c r="L72" s="267"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>2. Batch Traceability</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="40" customHeight="1">
+      <x:c r="A75" s="286" t="str">
+        <x:v>Module</x:v>
+      </x:c>
+      <x:c r="B75" s="286" t="str">
+        <x:v>Batch ID</x:v>
+      </x:c>
+      <x:c r="C75" s="286" t="str">
+        <x:v>Business Rule</x:v>
+      </x:c>
+      <x:c r="D75" s="286" t="str">
+        <x:v>Transaction正本・単位</x:v>
+      </x:c>
+      <x:c r="E75" s="286" t="str">
+        <x:v>Table / 外部資源</x:v>
+      </x:c>
+      <x:c r="F75" s="286" t="str">
+        <x:v>起動排他時のPossible Error</x:v>
+      </x:c>
+      <x:c r="G75" s="286" t="str">
+        <x:v>Message正本</x:v>
+      </x:c>
+      <x:c r="H75" s="286" t="str">
+        <x:v>詳細設計 / Test</x:v>
+      </x:c>
+      <x:c r="I75" s="286" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="110" customHeight="1">
+      <x:c r="A76" s="272" t="str">
+        <x:v>M12</x:v>
+      </x:c>
+      <x:c r="B76" s="272" t="str">
+        <x:v>BATCH-001</x:v>
+      </x:c>
+      <x:c r="C76" s="272" t="str">
+        <x:v>BR-BATCH-001, BR-NTF-001, BR-NTF-002</x:v>
+      </x:c>
+      <x:c r="D76" s="272" t="str">
+        <x:v>20／37_バッチ E8: Task単位（独立TX IDなし）</x:v>
+      </x:c>
+      <x:c r="E76" s="272" t="str">
+        <x:v>tasks, projects, employees, users, notifications</x:v>
+      </x:c>
+      <x:c r="F76" s="272" t="str">
+        <x:v>BATCH-5001</x:v>
+      </x:c>
+      <x:c r="G76" s="272" t="str">
+        <x:v>20／37の通知定義、18／32の共通例外</x:v>
+      </x:c>
+      <x:c r="H76" s="272" t="str">
+        <x:v>Batch詳細設計 / UT-BATCH-001 / IT-BATCH-001</x:v>
+      </x:c>
+      <x:c r="I76" s="272" t="str">
+        <x:v>多重起動時のみBATCH-5001。正常実行時はErrorなし。16／28 BR-BATCH-001、18／32 Batch排他例外、20／37 Batch起動制御を参照。処理開始後の失敗は20／37の各Batch定義に従う。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="110" customHeight="1">
+      <x:c r="A77" s="272" t="str">
+        <x:v>M12</x:v>
+      </x:c>
+      <x:c r="B77" s="272" t="str">
+        <x:v>BATCH-002</x:v>
+      </x:c>
+      <x:c r="C77" s="272" t="str">
+        <x:v>BR-BATCH-001, BR-NTF-001, BR-NTF-002</x:v>
+      </x:c>
+      <x:c r="D77" s="272" t="str">
+        <x:v>20／37_バッチ E9: Taskと通知を同一Transaction（独立TX IDなし）</x:v>
+      </x:c>
+      <x:c r="E77" s="272" t="str">
+        <x:v>tasks, projects, employees, users, notifications</x:v>
+      </x:c>
+      <x:c r="F77" s="272" t="str">
+        <x:v>BATCH-5001</x:v>
+      </x:c>
+      <x:c r="G77" s="272" t="str">
+        <x:v>20／37の通知定義、18／32の共通例外</x:v>
+      </x:c>
+      <x:c r="H77" s="272" t="str">
+        <x:v>Batch詳細設計 / UT-BATCH-002 / IT-BATCH-002</x:v>
+      </x:c>
+      <x:c r="I77" s="272" t="str">
+        <x:v>多重起動時のみBATCH-5001。正常実行時はErrorなし。16／28 BR-BATCH-001、18／32 Batch排他例外、20／37 Batch起動制御を参照。処理開始後の失敗は20／37の各Batch定義に従う。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="110" customHeight="1">
+      <x:c r="A78" s="272" t="str">
+        <x:v>M12</x:v>
+      </x:c>
+      <x:c r="B78" s="272" t="str">
+        <x:v>BATCH-003</x:v>
+      </x:c>
+      <x:c r="C78" s="272" t="str">
+        <x:v>BR-BATCH-001, BR-RPT-002, BR-RPT-005</x:v>
+      </x:c>
+      <x:c r="D78" s="272" t="str">
+        <x:v>20／37_バッチ E10: 通知1件単位（独立TX IDなし）</x:v>
+      </x:c>
+      <x:c r="E78" s="272" t="str">
+        <x:v>employees, users, projects, project_members, daily_reports, business_holidays, notifications</x:v>
+      </x:c>
+      <x:c r="F78" s="272" t="str">
+        <x:v>BATCH-5001</x:v>
+      </x:c>
+      <x:c r="G78" s="272" t="str">
+        <x:v>20／37の通知定義、18／32の共通例外</x:v>
+      </x:c>
+      <x:c r="H78" s="272" t="str">
+        <x:v>Batch詳細設計 / UT-BATCH-003 / IT-BATCH-003</x:v>
+      </x:c>
+      <x:c r="I78" s="272" t="str">
+        <x:v>多重起動時のみBATCH-5001。正常実行時はErrorなし。16／28 BR-BATCH-001、18／32 Batch排他例外、20／37 Batch起動制御を参照。処理開始後の失敗は20／37の各Batch定義に従う。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="110" customHeight="1">
+      <x:c r="A79" s="272" t="str">
+        <x:v>M12</x:v>
+      </x:c>
+      <x:c r="B79" s="272" t="str">
+        <x:v>BATCH-004</x:v>
+      </x:c>
+      <x:c r="C79" s="272" t="str">
+        <x:v>BR-BATCH-001, BR-NTF-001</x:v>
+      </x:c>
+      <x:c r="D79" s="272" t="str">
+        <x:v>20／37_バッチ E11: 500件削除単位（独立TX IDなし）</x:v>
+      </x:c>
+      <x:c r="E79" s="272" t="str">
+        <x:v>notifications</x:v>
+      </x:c>
+      <x:c r="F79" s="272" t="str">
+        <x:v>BATCH-5001</x:v>
+      </x:c>
+      <x:c r="G79" s="272" t="str">
+        <x:v>ユーザー表示なし。20／37の運用Log</x:v>
+      </x:c>
+      <x:c r="H79" s="272" t="str">
+        <x:v>Batch詳細設計 / UT-BATCH-004 / IT-BATCH-004</x:v>
+      </x:c>
+      <x:c r="I79" s="272" t="str">
+        <x:v>多重起動時のみBATCH-5001。正常実行時はErrorなし。16／28 BR-BATCH-001、18／32 Batch排他例外、20／37 Batch起動制御を参照。処理開始後の失敗は20／37の各Batch定義に従う。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="110" customHeight="1">
+      <x:c r="A80" s="272" t="str">
+        <x:v>M12</x:v>
+      </x:c>
+      <x:c r="B80" s="272" t="str">
+        <x:v>BATCH-005</x:v>
+      </x:c>
+      <x:c r="C80" s="272" t="str">
+        <x:v>BR-BATCH-001, BR-LOG-001</x:v>
+      </x:c>
+      <x:c r="D80" s="272" t="str">
+        <x:v>20／37_バッチ E12: 500件削除単位（独立TX IDなし）</x:v>
+      </x:c>
+      <x:c r="E80" s="272" t="str">
+        <x:v>operation_logs, login_histories</x:v>
+      </x:c>
+      <x:c r="F80" s="272" t="str">
+        <x:v>BATCH-5001</x:v>
+      </x:c>
+      <x:c r="G80" s="272" t="str">
+        <x:v>ユーザー表示なし。20／37の運用Log</x:v>
+      </x:c>
+      <x:c r="H80" s="272" t="str">
+        <x:v>Batch詳細設計 / UT-BATCH-005 / IT-BATCH-005</x:v>
+      </x:c>
+      <x:c r="I80" s="272" t="str">
+        <x:v>多重起動時のみBATCH-5001。正常実行時はErrorなし。16／28 BR-BATCH-001、18／32 Batch排他例外、20／37 Batch起動制御を参照。処理開始後の失敗は20／37の各Batch定義に従う。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="110" customHeight="1">
+      <x:c r="A81" s="272" t="str">
+        <x:v>M12</x:v>
+      </x:c>
+      <x:c r="B81" s="272" t="str">
+        <x:v>BATCH-006</x:v>
+      </x:c>
+      <x:c r="C81" s="272" t="str">
+        <x:v>BR-BATCH-001, BR-AUTH-001</x:v>
+      </x:c>
+      <x:c r="D81" s="272" t="str">
+        <x:v>20／37_バッチ E13: DB500件単位、Redisは外部処理（独立TX IDなし）</x:v>
+      </x:c>
+      <x:c r="E81" s="272" t="str">
+        <x:v>refresh_tokens / Redis</x:v>
+      </x:c>
+      <x:c r="F81" s="272" t="str">
+        <x:v>BATCH-5001</x:v>
+      </x:c>
+      <x:c r="G81" s="272" t="str">
+        <x:v>ユーザー表示なし。20／37の運用Log</x:v>
+      </x:c>
+      <x:c r="H81" s="272" t="str">
+        <x:v>Batch詳細設計 / UT-BATCH-006 / IT-BATCH-006</x:v>
+      </x:c>
+      <x:c r="I81" s="272" t="str">
+        <x:v>多重起動時のみBATCH-5001。正常実行時はErrorなし。16／28 BR-BATCH-001、18／32 Batch排他例外、20／37 Batch起動制御を参照。処理開始後の失敗は20／37の各Batch定義に従う。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I2"/>
     <x:mergeCell ref="A6:I6"/>
-    <x:mergeCell ref="A35:I36"/>
     <x:mergeCell ref="A71:I72"/>
     <x:mergeCell ref="A1:L2"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A71:L72"/>
+    <x:mergeCell ref="A74:L74"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5943,6 +7186,12 @@
       <x:c r="D1" s="77"/>
       <x:c r="E1" s="77"/>
       <x:c r="F1" s="77"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="77"/>
@@ -5951,6 +7200,12 @@
       <x:c r="D2" s="77"/>
       <x:c r="E2" s="77"/>
       <x:c r="F2" s="77"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="71" t="str">
@@ -5959,30 +7214,42 @@
       <x:c r="B3" s="72" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="71" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C3" s="275" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="D3" s="72" t="str">
         <x:v>CW-BD-006</x:v>
       </x:c>
       <x:c r="E3" s="72"/>
       <x:c r="F3" s="72"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="71" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="71" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D4" s="72" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E4" s="72"/>
       <x:c r="F4" s="72"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="73"/>
@@ -5991,6 +7258,12 @@
       <x:c r="D5" s="73"/>
       <x:c r="E5" s="73"/>
       <x:c r="F5" s="73"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="74" t="str">
@@ -6001,6 +7274,12 @@
       <x:c r="D6" s="74"/>
       <x:c r="E6" s="74"/>
       <x:c r="F6" s="74"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="75" t="str">
@@ -6021,6 +7300,12 @@
       <x:c r="F7" s="75" t="str">
         <x:v>状態</x:v>
       </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="76" t="str">
@@ -6036,11 +7321,17 @@
         <x:v>研修環境と長期Support</x:v>
       </x:c>
       <x:c r="E8" s="76" t="str">
-        <x:v>01/22/技術選型</x:v>
+        <x:v>01・20・技術選型</x:v>
       </x:c>
       <x:c r="F8" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="76" t="str">
@@ -6056,11 +7347,17 @@
         <x:v>DB差異をPG判断にしない</x:v>
       </x:c>
       <x:c r="E9" s="76" t="str">
-        <x:v>01/15～17/22</x:v>
+        <x:v>01・15・20</x:v>
       </x:c>
       <x:c r="F9" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="76" t="str">
@@ -6076,11 +7373,17 @@
         <x:v>同一APIで比較学習</x:v>
       </x:c>
       <x:c r="E10" s="76" t="str">
-        <x:v>01/04～09/22</x:v>
+        <x:v>01・04～09・20</x:v>
       </x:c>
       <x:c r="F10" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="76" t="str">
@@ -6101,6 +7404,12 @@
       <x:c r="F11" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="76" t="str">
@@ -6116,11 +7425,17 @@
         <x:v>方式統一</x:v>
       </x:c>
       <x:c r="E12" s="76" t="str">
-        <x:v>10/21</x:v>
+        <x:v>10・19</x:v>
       </x:c>
       <x:c r="F12" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="76" t="str">
@@ -6136,11 +7451,17 @@
         <x:v>PG判断差異防止</x:v>
       </x:c>
       <x:c r="E13" s="76" t="str">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F13" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="76" t="str">
@@ -6156,11 +7477,17 @@
         <x:v>研修運用基準</x:v>
       </x:c>
       <x:c r="E14" s="76" t="str">
-        <x:v>17/21/22</x:v>
+        <x:v>15・19・20</x:v>
       </x:c>
       <x:c r="F14" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="76" t="str">
@@ -6176,11 +7503,17 @@
         <x:v>Archiveは本期対象外</x:v>
       </x:c>
       <x:c r="E15" s="76" t="str">
-        <x:v>17/22</x:v>
+        <x:v>15・20</x:v>
       </x:c>
       <x:c r="F15" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="76" t="str">
@@ -6196,11 +7529,17 @@
         <x:v>日報期限/未提出Batch共通化</x:v>
       </x:c>
       <x:c r="E16" s="76" t="str">
-        <x:v>17/18/22</x:v>
+        <x:v>15・16・20</x:v>
       </x:c>
       <x:c r="F16" s="76" t="str">
         <x:v>確定</x:v>
       </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="76" t="str">
@@ -6229,4 +7568,202 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="92" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="279" t="str">
+        <x:v>07_設計正本対応</x:v>
+      </x:c>
+      <x:c r="B1" s="278"/>
+      <x:c r="C1" s="278"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="278"/>
+      <x:c r="B2" s="278"/>
+      <x:c r="C2" s="278"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="278" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="278"/>
+      <x:c r="C3" s="278"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="278"/>
+      <x:c r="B4" s="278"/>
+      <x:c r="C4" s="278"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="278" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="278"/>
+      <x:c r="C5" s="278"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="278"/>
+      <x:c r="B6" s="278"/>
+      <x:c r="C6" s="278"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="281" t="str">
+        <x:v>設計事項</x:v>
+      </x:c>
+      <x:c r="B7" s="281" t="str">
+        <x:v>正本</x:v>
+      </x:c>
+      <x:c r="C7" s="281" t="str">
+        <x:v>他文書の扱い</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="283" t="str">
+        <x:v>Role/Permission/Data Scope</x:v>
+      </x:c>
+      <x:c r="B8" s="283" t="str">
+        <x:v>02／09～14</x:v>
+      </x:c>
+      <x:c r="C8" s="283" t="str">
+        <x:v>Permission/DS IDを参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="282" t="str">
+        <x:v>画面一覧/Route/遷移</x:v>
+      </x:c>
+      <x:c r="B9" s="282" t="str">
+        <x:v>03／12・13・20・22</x:v>
+      </x:c>
+      <x:c r="C9" s="282" t="str">
+        <x:v>04～09は固有項目/処理/WF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="283" t="str">
+        <x:v>Validation共通</x:v>
+      </x:c>
+      <x:c r="B10" s="283" t="str">
+        <x:v>03／16・21</x:v>
+      </x:c>
+      <x:c r="C10" s="283" t="str">
+        <x:v>画面固有値とVAL IDのみ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="282" t="str">
+        <x:v>API Contract</x:v>
+      </x:c>
+      <x:c r="B11" s="282" t="str">
+        <x:v>10～14／23_API項目定義</x:v>
+      </x:c>
+      <x:c r="C11" s="282" t="str">
+        <x:v>Sampleは参考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="283" t="str">
+        <x:v>API Error Code/HTTP</x:v>
+      </x:c>
+      <x:c r="B12" s="283" t="str">
+        <x:v>10～14／21_エラーコード</x:v>
+      </x:c>
+      <x:c r="C12" s="283" t="str">
+        <x:v>共通/Authは10、Domainは各分冊</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="282" t="str">
+        <x:v>DB構造</x:v>
+      </x:c>
+      <x:c r="B13" s="282" t="str">
+        <x:v>15_DB基本設計書</x:v>
+      </x:c>
+      <x:c r="C13" s="282" t="str">
+        <x:v>API Mappingから参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="283" t="str">
+        <x:v>Status/業務Rule</x:v>
+      </x:c>
+      <x:c r="B14" s="283" t="str">
+        <x:v>16／26～28</x:v>
+      </x:c>
+      <x:c r="C14" s="283" t="str">
+        <x:v>DBは型/制約と状態ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="282" t="str">
+        <x:v>Transaction/排他</x:v>
+      </x:c>
+      <x:c r="B15" s="282" t="str">
+        <x:v>17／29・30</x:v>
+      </x:c>
+      <x:c r="C15" s="282" t="str">
+        <x:v>TX IDを参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="105" customHeight="1">
+      <x:c r="A16" s="283" t="str">
+        <x:v>画面・Validation・API Error Message／例外</x:v>
+      </x:c>
+      <x:c r="B16" s="283" t="str">
+        <x:v>18／31・31B・31V・32</x:v>
+      </x:c>
+      <x:c r="C16" s="283" t="str">
+        <x:v>画面MessageはMessage IDで参照。Batch内部排他例外は18／32。Batch通知Template本文は20／37を正本とし本書へ複製しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="282" t="str">
+        <x:v>Log/File/Redis/Security</x:v>
+      </x:c>
+      <x:c r="B17" s="282" t="str">
+        <x:v>19／33～36</x:v>
+      </x:c>
+      <x:c r="C17" s="282" t="str">
+        <x:v>定義を重複維持しない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="283" t="str">
+        <x:v>Batch/非機能</x:v>
+      </x:c>
+      <x:c r="B18" s="283" t="str">
+        <x:v>20／37～40</x:v>
+      </x:c>
+      <x:c r="C18" s="283" t="str">
+        <x:v>Mandatory/Targetを区別</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="85" customHeight="1">
+      <x:c r="A19" s="272" t="str">
+        <x:v>Batch通知Template</x:v>
+      </x:c>
+      <x:c r="B19" s="272" t="str">
+        <x:v>20_バッチ非機能運用_基本設計書／37_バッチ</x:v>
+      </x:c>
+      <x:c r="C19" s="272" t="str">
+        <x:v>Batch通知の件名・本文Templateを管理。18には重複定義しない。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A3:C3"/>
+    <x:mergeCell ref="A5:C5"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/基本設計/00_基本設計書総合管理.xlsx
+++ b/基本設計/00_基本設計書総合管理.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R0324d1e50c29418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Re058c3dbba404a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R6be70d4c6283460a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="R6a8b729516014b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="R30e057ef1fec4d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="Rf4afefcdf14144ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R03ecfeec461349ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="R12aab8f26d2240b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R42b3a6393b4546cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R6210151e3aec4bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R8560cfa52c474220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="R22fbd29d83854f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="Rbd12cc56e2d84db9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R284bf00f2c444493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R1a67a506e812461d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="R7d42d17b85e8474e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       <x:name val="Yu Gothic"/>
     </x:font>
   </x:fonts>
-  <x:fills count="38">
+  <x:fills count="39">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -361,6 +361,11 @@
         <x:fgColor rgb="FF234F77"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="9">
     <x:border/>
@@ -438,7 +443,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="289">
+  <x:cellXfs count="291">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1046,6 +1051,8 @@
     <x:xf numFmtId="0" fontId="11" fillId="37" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1493,7 +1500,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="265" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1530,10 +1537,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="270" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="E13" s="222"/>
-      <x:c r="F13" s="222"/>
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="E13" s="222" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="F13" s="222" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
       <x:c r="G13"/>
       <x:c r="H13"/>
       <x:c r="I13"/>
@@ -1548,10 +1559,14 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="270" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="E14" s="222"/>
-      <x:c r="F14" s="222"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="E14" s="222" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F14" s="222" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="G14"/>
       <x:c r="H14"/>
       <x:c r="I14"/>
@@ -1584,10 +1599,14 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="D16" s="270" t="str">
-        <x:v>Review中</x:v>
-      </x:c>
-      <x:c r="E16" s="222"/>
-      <x:c r="F16" s="222"/>
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="E16" s="222" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F16" s="222" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
       <x:c r="G16"/>
       <x:c r="H16"/>
       <x:c r="I16"/>
@@ -1617,31 +1636,73 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
+      <x:c r="B19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
+      <x:c r="B20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="B21" s="264"/>
-      <x:c r="C21" s="264"/>
-      <x:c r="D21" s="264"/>
-      <x:c r="E21" s="264"/>
-      <x:c r="F21" s="264"/>
-      <x:c r="G21" s="264"/>
-      <x:c r="H21" s="264"/>
+      <x:c r="B21" s="264" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C21" s="264" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D21" s="264" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E21" s="264" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F21" s="264" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G21" s="264" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H21" s="264" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="B22"/>
@@ -1745,15 +1806,29 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="B4" s="72"/>
-      <x:c r="C4" s="72"/>
-      <x:c r="D4" s="275"/>
-      <x:c r="E4" s="72"/>
-      <x:c r="F4" s="72"/>
-      <x:c r="G4" s="72"/>
-      <x:c r="H4" s="72"/>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="72" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="C4" s="72" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="D4" s="275" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="E4" s="72" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="72" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="G4" s="72" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="H4" s="72" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="I4"/>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -2247,6 +2322,32 @@
       </x:c>
       <x:c r="H22" s="272" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="115" customHeight="1">
+      <x:c r="A23" s="266" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B23" s="266" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="C23" s="266" t="str">
+        <x:v>ログイン試行制限の独立固定窓、5回目Lock成立・満了後再開を明確化。CHG-AUTH-20260928-01</x:v>
+      </x:c>
+      <x:c r="D23" s="266" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E23" s="266" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F23" s="266" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G23" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H23" s="266" t="str">
+        <x:v>変更指示に基づく改訂。新Baseline承認は別途記録。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2324,18 +2425,26 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="273" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="274" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
       <x:c r="E4" s="273" t="str">
-        <x:v>作成日：2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="35"/>
-      <x:c r="G4" s="36"/>
+        <x:v>作成日：2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="35" t="str">
+        <x:v>作成日：2026-09-28</x:v>
+      </x:c>
+      <x:c r="G4" s="36" t="str">
+        <x:v>作成日：2026-09-28</x:v>
+      </x:c>
       <x:c r="H4"/>
       <x:c r="I4"/>
       <x:c r="J4"/>
@@ -2748,13 +2857,17 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="160"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="160" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="275" t="str">
-        <x:v>改訂日：2026-09-24</x:v>
-      </x:c>
-      <x:c r="D4" s="160"/>
+        <x:v>改訂日：2026-09-28</x:v>
+      </x:c>
+      <x:c r="D4" s="160" t="str">
+        <x:v>改訂日：2026-09-28</x:v>
+      </x:c>
       <x:c r="E4" s="160"/>
       <x:c r="F4" s="160"/>
       <x:c r="G4"/>
@@ -3617,17 +3730,31 @@
       <x:c r="K4"/>
       <x:c r="L4"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="35" customHeight="1">
       <x:c r="A5" s="278" t="str">
-        <x:v>BL-2026-09-24 / Review中</x:v>
-      </x:c>
-      <x:c r="B5" s="278"/>
-      <x:c r="C5" s="278"/>
-      <x:c r="D5" s="278"/>
-      <x:c r="E5" s="278"/>
-      <x:c r="F5" s="278"/>
-      <x:c r="G5" s="278"/>
-      <x:c r="H5" s="278"/>
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
+      <x:c r="B5" s="278" t="str">
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
+      <x:c r="C5" s="278" t="str">
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
+      <x:c r="D5" s="278" t="str">
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
+      <x:c r="E5" s="278" t="str">
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
+      <x:c r="F5" s="278" t="str">
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
+      <x:c r="G5" s="278" t="str">
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
+      <x:c r="H5" s="278" t="str">
+        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+      </x:c>
       <x:c r="I5"/>
       <x:c r="J5"/>
       <x:c r="K5"/>
@@ -3691,13 +3818,13 @@
         <x:v>基本設計書総合管理</x:v>
       </x:c>
       <x:c r="E8" s="283" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F8" s="283" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G8" s="283" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H8" s="283" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -3991,13 +4118,13 @@
         <x:v>API共通と認証_基本設計書</x:v>
       </x:c>
       <x:c r="E18" s="283" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F18" s="283" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G18" s="283" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H18" s="283" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4171,13 +4298,13 @@
         <x:v>業務ルールと状態遷移_基本設計書</x:v>
       </x:c>
       <x:c r="E24" s="283" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F24" s="283" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G24" s="283" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H24" s="283" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4261,13 +4388,13 @@
         <x:v>ログファイルRedisセキュリティ_基本設計書</x:v>
       </x:c>
       <x:c r="E27" s="282" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F27" s="282" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G27" s="282" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H27" s="282" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4458,7 +4585,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="160"/>
       <x:c r="D4" s="160"/>
@@ -4467,7 +4594,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="G4" s="72" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-28</x:v>
       </x:c>
       <x:c r="H4" s="160"/>
       <x:c r="I4" s="160"/>
@@ -7234,13 +7361,13 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="71" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D4" s="72" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-28</x:v>
       </x:c>
       <x:c r="E4" s="72"/>
       <x:c r="F4" s="72"/>
@@ -7559,6 +7686,86 @@
       </x:c>
       <x:c r="F17" s="76" t="str">
         <x:v>確定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="30" customHeight="1">
+      <x:c r="A19" s="290" t="str">
+        <x:v>変更ID</x:v>
+      </x:c>
+      <x:c r="B19" s="290" t="str">
+        <x:v>分類</x:v>
+      </x:c>
+      <x:c r="C19" s="290" t="str">
+        <x:v>変更内容／正本</x:v>
+      </x:c>
+      <x:c r="D19" s="290" t="str">
+        <x:v>理由／影響</x:v>
+      </x:c>
+      <x:c r="E19" s="290" t="str">
+        <x:v>対象文書</x:v>
+      </x:c>
+      <x:c r="F19" s="290" t="str">
+        <x:v>状態</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="145" customHeight="1">
+      <x:c r="A20" s="266" t="str">
+        <x:v>CHG-AUTH-20260928-01</x:v>
+      </x:c>
+      <x:c r="B20" s="266" t="str">
+        <x:v>認証仕様明確化</x:v>
+      </x:c>
+      <x:c r="C20" s="266" t="str">
+        <x:v>正本：16／28 BR-AUTH-002（Lock）、19／35・36（試行制限）、10／21（HTTP）。JSON契約・Code体系・制限値は維持。</x:v>
+      </x:c>
+      <x:c r="D20" s="266" t="str">
+        <x:v>5回目の外部応答と満了後Resetを統一。IP/User独立60秒固定窓を確定。</x:v>
+      </x:c>
+      <x:c r="E20" s="266" t="str">
+        <x:v>基本設計10・16・19／SCR-001／API-AUTH-001</x:v>
+      </x:c>
+      <x:c r="F20" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="145" customHeight="1">
+      <x:c r="A21" s="266" t="str">
+        <x:v>影響調査</x:v>
+      </x:c>
+      <x:c r="B21" s="266" t="str">
+        <x:v>変更範囲</x:v>
+      </x:c>
+      <x:c r="C21" s="266" t="str">
+        <x:v>DB構造・Permission・Route・Message ID変更なし。SQL-04、Redis、Error Mapping、UTへ反映。</x:v>
+      </x:c>
+      <x:c r="D21" s="266" t="str">
+        <x:v>既存Baselineを上書き承認せず原版Backup、Ver.2.6の差分を管理。</x:v>
+      </x:c>
+      <x:c r="E21" s="266" t="str">
+        <x:v>00文書一覧に改訂登録。その他17本はVer.2.5維持。</x:v>
+      </x:c>
+      <x:c r="F21" s="266" t="str">
+        <x:v>調査済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="145" customHeight="1">
+      <x:c r="A22" s="266" t="str">
+        <x:v>承認管理</x:v>
+      </x:c>
+      <x:c r="B22" s="266" t="str">
+        <x:v>変更後Review</x:v>
+      </x:c>
+      <x:c r="C22" s="266" t="str">
+        <x:v>変更指示：2026-09-28 SCR-001／API-AUTH-001 Review修正指示。対応結果とCross Reviewを品質管理資料へ記録。</x:v>
+      </x:c>
+      <x:c r="D22" s="266" t="str">
+        <x:v>変更内容の採用指示と成果物承認を区別。最終承認者・承認日はLeaderが記録。</x:v>
+      </x:c>
+      <x:c r="E22" s="266" t="str">
+        <x:v>基準BL-2026-09-24／承認後にBaseline更新</x:v>
+      </x:c>
+      <x:c r="F22" s="266" t="str">
+        <x:v>承認待ち</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/基本設計/00_基本設計書総合管理.xlsx
+++ b/基本設計/00_基本設計書総合管理.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R42b3a6393b4546cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R6210151e3aec4bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R8560cfa52c474220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="R22fbd29d83854f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="Rbd12cc56e2d84db9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R284bf00f2c444493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R1a67a506e812461d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="R7d42d17b85e8474e"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R7872c79655e0403f"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R85afdf1e4efa4b66"/>
+    <ns0:sheet name="03_用語集" sheetId="4" ns1:id="R58b6911dcd9c47a2"/>
+    <ns0:sheet name="04_前提条件" sheetId="5" ns1:id="R269a5d944ba14d8a"/>
+    <ns0:sheet name="02_文書一覧" sheetId="49" ns1:id="R68cc85942e7a4b0c"/>
+    <ns0:sheet name="05_トレーサビリティ" sheetId="50" ns1:id="R84c06b13c71c499f"/>
+    <ns0:sheet name="06_設計決定事項" sheetId="51" ns1:id="Rd999d509a6724489"/>
+    <ns0:sheet name="07_設計正本対応" sheetId="52" ns1:id="Ra9bfa43d6e91400b"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="27">
+  <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -171,6 +171,11 @@
       <x:b/>
       <x:sz val="17"/>
       <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF172B40"/>
       <x:name val="Yu Gothic"/>
     </x:font>
   </x:fonts>
@@ -367,7 +372,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="10">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -439,11 +444,25 @@
         <x:color rgb="FFD4DEE8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="291">
+  <x:cellXfs count="294">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1053,6 +1072,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1500,7 +1528,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="265" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.8</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1537,7 +1565,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="270" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.8</x:v>
       </x:c>
       <x:c r="E13" s="222" t="str">
         <x:v>Ver.2.6</x:v>
@@ -1559,7 +1587,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="270" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E14" s="222" t="str">
         <x:v>2026-09-28</x:v>
@@ -1634,10 +1662,10 @@
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="55" customHeight="1">
       <x:c r="A19"/>
-      <x:c r="B19" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      <x:c r="B19" s="265" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。CHG-AUTH-20260928-01／CHG-MENU-20260929-01／CHG-DB-20260929-01を反映。物理外鍵非採用。正式承認・次Baseline登録は別途。</x:v>
       </x:c>
       <x:c r="C19" t="str">
         <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
@@ -1806,7 +1834,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.8    改訂日：2026-09-29    基準Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
         <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
@@ -2348,6 +2376,58 @@
       </x:c>
       <x:c r="H23" s="266" t="str">
         <x:v>変更指示に基づく改訂。新Baseline承認は別途記録。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="95" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>Ver.2.7</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>方式合意に基づく補完。成果物の正式承認は別途。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="70" customHeight="1">
+      <x:c r="A25" s="293" t="str">
+        <x:v>Ver.2.8</x:v>
+      </x:c>
+      <x:c r="B25" s="293" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C25" s="293" t="str">
+        <x:v>CHG-DB-20260929-01：15/17、DB01/01Eを物理外鍵非採用へ同期。PK/UK/Null/CHECK/Index維持。</x:v>
+      </x:c>
+      <x:c r="D25" s="293" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E25" s="293" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F25" s="293" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G25" s="293" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H25" s="293" t="str">
+        <x:v>ユーザー変更指示。正式承認は別途。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2425,19 +2505,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="273" t="str">
-        <x:v>版数：Ver.2.6</x:v>
+        <x:v>版数：Ver.2.7</x:v>
       </x:c>
       <x:c r="B4" s="23" t="str">
         <x:v>版数：Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="274" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="D4" s="21" t="str">
         <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="E4" s="273" t="str">
-        <x:v>作成日：2026-09-28</x:v>
+        <x:v>作成日：2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="35" t="str">
         <x:v>作成日：2026-09-28</x:v>
@@ -2857,13 +2937,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.6</x:v>
+        <x:v>版数：Ver.2.7</x:v>
       </x:c>
       <x:c r="B4" s="160" t="str">
         <x:v>版数：Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="275" t="str">
-        <x:v>改訂日：2026-09-28</x:v>
+        <x:v>改訂日：2026-09-29</x:v>
       </x:c>
       <x:c r="D4" s="160" t="str">
         <x:v>改訂日：2026-09-28</x:v>
@@ -3730,9 +3810,9 @@
       <x:c r="K4"/>
       <x:c r="L4"/>
     </x:row>
-    <x:row r="5" ht="35" customHeight="1">
+    <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
+        <x:v>基準BL-2026-09-24。個別変更AUTH/MENUおよびCHG-DB-20260929-01を含む。Document Versionは各行を正とし、正式承認は別途記録。</x:v>
       </x:c>
       <x:c r="B5" s="278" t="str">
         <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
@@ -3818,7 +3898,7 @@
         <x:v>基本設計書総合管理</x:v>
       </x:c>
       <x:c r="E8" s="283" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.8</x:v>
       </x:c>
       <x:c r="F8" s="283" t="str">
         <x:v>修正済</x:v>
@@ -3878,13 +3958,13 @@
         <x:v>権限基本設計書</x:v>
       </x:c>
       <x:c r="E10" s="283" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F10" s="283" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G10" s="283" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H10" s="283" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4118,7 +4198,7 @@
         <x:v>API共通と認証_基本設計書</x:v>
       </x:c>
       <x:c r="E18" s="283" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="F18" s="283" t="str">
         <x:v>修正済</x:v>
@@ -4268,13 +4348,13 @@
         <x:v>DB基本設計書</x:v>
       </x:c>
       <x:c r="E23" s="282" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F23" s="282" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G23" s="282" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H23" s="282" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4328,13 +4408,13 @@
         <x:v>トランザクションと排他_基本設計書</x:v>
       </x:c>
       <x:c r="E25" s="282" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F25" s="282" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G25" s="282" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H25" s="282" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4585,7 +4665,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="160"/>
       <x:c r="D4" s="160"/>
@@ -4594,7 +4674,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="G4" s="72" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="H4" s="160"/>
       <x:c r="I4" s="160"/>
@@ -7361,13 +7441,13 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="71" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D4" s="72" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E4" s="72"/>
       <x:c r="F4" s="72"/>

--- a/基本設計/00_基本設計書総合管理.xlsx
+++ b/基本設計/00_基本設計書総合管理.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R7872c79655e0403f"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R85afdf1e4efa4b66"/>
-    <ns0:sheet name="03_用語集" sheetId="4" ns1:id="R58b6911dcd9c47a2"/>
-    <ns0:sheet name="04_前提条件" sheetId="5" ns1:id="R269a5d944ba14d8a"/>
-    <ns0:sheet name="02_文書一覧" sheetId="49" ns1:id="R68cc85942e7a4b0c"/>
-    <ns0:sheet name="05_トレーサビリティ" sheetId="50" ns1:id="R84c06b13c71c499f"/>
-    <ns0:sheet name="06_設計決定事項" sheetId="51" ns1:id="Rd999d509a6724489"/>
-    <ns0:sheet name="07_設計正本対応" sheetId="52" ns1:id="Ra9bfa43d6e91400b"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R695279477bad40e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rff1d8bd31f8949a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R54a97e8d7a9244db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="Rca30d8a25b5d4423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="Ra5ad7404b7f44989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R15a5a987134f432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="Re1345a45099a459f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="R7d538cdaedca49ab"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="28">
+  <x:fonts count="29">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -178,8 +178,13 @@
       <x:color rgb="FF172B40"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Meiryo"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="39">
+  <x:fills count="40">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -371,8 +376,13 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="11">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -458,11 +468,25 @@
         <x:color rgb="FFD9E2EC"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="294">
+  <x:cellXfs count="299">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1079,6 +1103,15 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1528,7 +1561,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="265" t="str">
-        <x:v>Ver.2.8</x:v>
+        <x:v>Ver.2.12</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1565,14 +1598,10 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="270" t="str">
-        <x:v>Ver.2.8</x:v>
-      </x:c>
-      <x:c r="E13" s="222" t="str">
-        <x:v>Ver.2.6</x:v>
-      </x:c>
-      <x:c r="F13" s="222" t="str">
-        <x:v>Ver.2.6</x:v>
-      </x:c>
+        <x:v>Ver.2.12</x:v>
+      </x:c>
+      <x:c r="E13" s="222"/>
+      <x:c r="F13" s="222"/>
       <x:c r="G13"/>
       <x:c r="H13"/>
       <x:c r="I13"/>
@@ -1587,14 +1616,10 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="270" t="str">
-        <x:v>2026-09-29</x:v>
-      </x:c>
-      <x:c r="E14" s="222" t="str">
-        <x:v>2026-09-28</x:v>
-      </x:c>
-      <x:c r="F14" s="222" t="str">
-        <x:v>2026-09-28</x:v>
-      </x:c>
+        <x:v>2026-10-08</x:v>
+      </x:c>
+      <x:c r="E14" s="222"/>
+      <x:c r="F14" s="222"/>
       <x:c r="G14"/>
       <x:c r="H14"/>
       <x:c r="I14"/>
@@ -1629,12 +1654,8 @@
       <x:c r="D16" s="270" t="str">
         <x:v>修正済</x:v>
       </x:c>
-      <x:c r="E16" s="222" t="str">
-        <x:v>修正済</x:v>
-      </x:c>
-      <x:c r="F16" s="222" t="str">
-        <x:v>修正済</x:v>
-      </x:c>
+      <x:c r="E16" s="222"/>
+      <x:c r="F16" s="222"/>
       <x:c r="G16"/>
       <x:c r="H16"/>
       <x:c r="I16"/>
@@ -1649,6 +1670,12 @@
       <x:c r="D17" s="272"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
       <x:c r="A18" s="272"/>
@@ -1661,78 +1688,61 @@
       </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19" ht="55" customHeight="1">
       <x:c r="A19"/>
       <x:c r="B19" s="265" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。CHG-AUTH-20260928-01／CHG-MENU-20260929-01／CHG-DB-20260929-01を反映。物理外鍵非採用。正式承認・次Baseline登録は別途。</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="F19" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="G19" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="H19" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
+        <x:v>基準Baseline：BL-2026-09-24。CHG-AUTH-20260928-01／CHG-MENU-20260929-01／CHG-DB-20260929-01を反映。物理外鍵非採用。正式承認・次Baseline登録は別途。 CHG-BATCH-20260930-01：Batch実行規約・通知ID採番を反映。
+CHG-ACTOR-20261007-01：Task関連の報告者・操作者ID定義を11・13・15・17へ反映。
+CHG-MIG-20261007-01：DB詳細設計ごとのFlyway Version帯を確定。正式Baseline更新は承認後とする。</x:v>
+      </x:c>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="F20" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="G20" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="B21" s="264" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="C21" s="264" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="D21" s="264" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="E21" s="264" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="F21" s="264" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="G21" s="264" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
-      <x:c r="H21" s="264" t="str">
-        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
-      </x:c>
+      <x:c r="A21"/>
+      <x:c r="B21" s="264"/>
+      <x:c r="C21" s="264"/>
+      <x:c r="D21" s="264"/>
+      <x:c r="E21" s="264"/>
+      <x:c r="F21" s="264"/>
+      <x:c r="G21" s="264"/>
+      <x:c r="H21" s="264"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
+      <x:c r="A22"/>
       <x:c r="B22"/>
       <x:c r="C22"/>
       <x:c r="D22"/>
@@ -1740,31 +1750,47 @@
       <x:c r="F22"/>
       <x:c r="G22"/>
       <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
+      <x:c r="A23"/>
       <x:c r="B23"/>
       <x:c r="C23"/>
       <x:c r="D23"/>
       <x:c r="E23"/>
       <x:c r="F23"/>
       <x:c r="G23"/>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
+      <x:c r="A24"/>
       <x:c r="B24"/>
       <x:c r="C24"/>
       <x:c r="D24"/>
       <x:c r="E24"/>
       <x:c r="F24"/>
       <x:c r="G24"/>
+      <x:c r="H24"/>
+      <x:c r="I24"/>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="B3:H5"/>
     <x:mergeCell ref="B8:H10"/>
     <x:mergeCell ref="D12:F12"/>
+    <x:mergeCell ref="D15:F15"/>
     <x:mergeCell ref="D13:F13"/>
     <x:mergeCell ref="D14:F14"/>
-    <x:mergeCell ref="D15:F15"/>
     <x:mergeCell ref="D16:F16"/>
     <x:mergeCell ref="B19:H21"/>
   </x:mergeCells>
@@ -1834,29 +1860,15 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.8    改訂日：2026-09-29    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="B4" s="72" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="C4" s="72" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="D4" s="275" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="E4" s="72" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="72" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="G4" s="72" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="H4" s="72" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
-      </x:c>
+        <x:v>版数：Ver.2.12    改訂日：2026-10-08    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="72"/>
+      <x:c r="C4" s="72"/>
+      <x:c r="D4" s="275"/>
+      <x:c r="E4" s="72"/>
+      <x:c r="F4" s="72"/>
+      <x:c r="G4" s="72"/>
+      <x:c r="H4" s="72"/>
       <x:c r="I4"/>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -2429,6 +2441,120 @@
       <x:c r="H25" s="293" t="str">
         <x:v>ユーザー変更指示。正式承認は別途。</x:v>
       </x:c>
+    </x:row>
+    <x:row r="26" ht="100" customHeight="1">
+      <x:c r="A26" s="298" t="str">
+        <x:v>Ver.2.9</x:v>
+      </x:c>
+      <x:c r="B26" s="298" t="str">
+        <x:v>2026-09-30</x:v>
+      </x:c>
+      <x:c r="C26" s="298" t="str">
+        <x:v>CHG-BATCH-20260930-01：BATCH-001実行/Timeout/監視/Retryとnotifications.id Identityを確定。関連文書を同期。</x:v>
+      </x:c>
+      <x:c r="D26" s="298" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E26" s="298" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F26" s="298" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G26" s="298" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H26" s="298" t="str">
+        <x:v>Review修正指示反映。基準Baselineは維持、正式承認は別途。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="34" customHeight="1">
+      <x:c r="A27" s="265" t="str">
+        <x:v>Ver.2.10</x:v>
+      </x:c>
+      <x:c r="B27" s="265" t="str">
+        <x:v>2026-10-07</x:v>
+      </x:c>
+      <x:c r="C27" s="265" t="str">
+        <x:v>CHG-ACTOR-20261007-01：Task関連の報告者・操作者IDの論理参照先、API設定元、Transactionを確定。</x:v>
+      </x:c>
+      <x:c r="D27" s="265" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E27" s="265" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F27" s="265" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G27" s="265" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H27" s="265" t="str">
+        <x:v>13・15・17を同期。基準Baselineは維持。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="60" customHeight="1">
+      <x:c r="A28" s="266" t="str">
+        <x:v>Ver.2.11</x:v>
+      </x:c>
+      <x:c r="B28" s="266" t="str">
+        <x:v>2026-10-07</x:v>
+      </x:c>
+      <x:c r="C28" s="266" t="str">
+        <x:v>CHG-MIG-20261007-01：DB-DD-01=V101～V110、DB-DD-02=V201～V210、DB-DD-03=V301～V310のMigration Version帯を確定。操作者IDの関連Table追跡も同期。 API/TX関連Table、全Sheet版数、Baseline・日付・印刷設定の再Review残項を補完。</x:v>
+      </x:c>
+      <x:c r="D28" s="266" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E28" s="266" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F28" s="266" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G28" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H28" s="266" t="str">
+        <x:v>詳細設計書書写規範と同期。基準Baselineは維持。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A29" s="266" t="str">
+        <x:v>Ver.2.12</x:v>
+      </x:c>
+      <x:c r="B29" s="266" t="str">
+        <x:v>2026-10-08</x:v>
+      </x:c>
+      <x:c r="C29" s="266" t="str">
+        <x:v>CHG-NTF-20261008-01：通知relatedTypeをTASK／PROJECT／SYSTEMへ統一。APIとDBの文書版数を同期。</x:v>
+      </x:c>
+      <x:c r="D29" s="266" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E29" s="266" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F29" s="266" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G29" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H29" s="266" t="str">
+        <x:v>14・15・16・20の通知関連仕様を整合。基準Baselineは維持。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2496,7 +2622,7 @@
         <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
-      <x:c r="G3" t="str"/>
+      <x:c r="G3"/>
       <x:c r="H3"/>
       <x:c r="I3"/>
       <x:c r="J3"/>
@@ -2505,26 +2631,18 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="273" t="str">
-        <x:v>版数：Ver.2.7</x:v>
-      </x:c>
-      <x:c r="B4" s="23" t="str">
-        <x:v>版数：Ver.2.6</x:v>
-      </x:c>
+        <x:v>版数：Ver.2.11</x:v>
+      </x:c>
+      <x:c r="B4" s="23"/>
       <x:c r="C4" s="274" t="str">
-        <x:v>Ver.2.7</x:v>
-      </x:c>
-      <x:c r="D4" s="21" t="str">
-        <x:v>Ver.2.6</x:v>
-      </x:c>
+        <x:v>Ver.2.11</x:v>
+      </x:c>
+      <x:c r="D4" s="21"/>
       <x:c r="E4" s="273" t="str">
-        <x:v>作成日：2026-09-29</x:v>
-      </x:c>
-      <x:c r="F4" s="35" t="str">
-        <x:v>作成日：2026-09-28</x:v>
-      </x:c>
-      <x:c r="G4" s="36" t="str">
-        <x:v>作成日：2026-09-28</x:v>
-      </x:c>
+        <x:v>作成日：2026-10-07</x:v>
+      </x:c>
+      <x:c r="F4" s="35"/>
+      <x:c r="G4" s="36"/>
       <x:c r="H4"/>
       <x:c r="I4"/>
       <x:c r="J4"/>
@@ -2866,9 +2984,9 @@
     <x:mergeCell ref="C3:D3"/>
     <x:mergeCell ref="E3:F3"/>
     <x:mergeCell ref="F3:G3"/>
+    <x:mergeCell ref="A6:F6"/>
     <x:mergeCell ref="A4:B4"/>
     <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="A6:F6"/>
     <x:mergeCell ref="E4:G4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2921,11 +3039,11 @@
       <x:c r="A3" s="200" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="160" t="str"/>
+      <x:c r="B3" s="160"/>
       <x:c r="C3" s="275" t="str">
         <x:v>章ID</x:v>
       </x:c>
-      <x:c r="D3" s="160" t="str"/>
+      <x:c r="D3" s="160"/>
       <x:c r="E3" s="160"/>
       <x:c r="F3" s="160"/>
       <x:c r="G3"/>
@@ -2937,17 +3055,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.7</x:v>
-      </x:c>
-      <x:c r="B4" s="160" t="str">
-        <x:v>版数：Ver.2.6</x:v>
-      </x:c>
+        <x:v>版数：Ver.2.11</x:v>
+      </x:c>
+      <x:c r="B4" s="160"/>
       <x:c r="C4" s="275" t="str">
-        <x:v>改訂日：2026-09-29</x:v>
-      </x:c>
-      <x:c r="D4" s="160" t="str">
-        <x:v>改訂日：2026-09-28</x:v>
-      </x:c>
+        <x:v>改訂日：2026-10-07</x:v>
+      </x:c>
+      <x:c r="D4" s="160"/>
       <x:c r="E4" s="160"/>
       <x:c r="F4" s="160"/>
       <x:c r="G4"/>
@@ -3605,10 +3719,10 @@
         <x:v>日報削除後</x:v>
       </x:c>
       <x:c r="C35" s="266" t="str">
-        <x:v>正本参照：16／28 BR-RPT-001、15／08_FK・Constraint</x:v>
+        <x:v>正本参照：16／28 BR-RPT-001、15／08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D35" s="266" t="str">
-        <x:v>16／28 BR-RPT-001、15／08_FK・Constraint</x:v>
+        <x:v>16／28 BR-RPT-001、15／08_論理参照・制約</x:v>
       </x:c>
       <x:c r="E35" s="266" t="str">
         <x:v>修正済</x:v>
@@ -3724,13 +3838,13 @@
     <x:mergeCell ref="C3:D3"/>
     <x:mergeCell ref="E3:F3"/>
     <x:mergeCell ref="F3:G3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
     <x:mergeCell ref="E4:F4"/>
     <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="A6:F6"/>
     <x:mergeCell ref="A25:F25"/>
     <x:mergeCell ref="A26:F26"/>
+    <x:mergeCell ref="A4:B4"/>
+    <x:mergeCell ref="C4:D4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3812,29 +3926,16 @@
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。個別変更AUTH/MENUおよびCHG-DB-20260929-01を含む。Document Versionは各行を正とし、正式承認は別途記録。</x:v>
-      </x:c>
-      <x:c r="B5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
-      </x:c>
-      <x:c r="C5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
-      </x:c>
-      <x:c r="D5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
-      </x:c>
-      <x:c r="E5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
-      </x:c>
-      <x:c r="F5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
-      </x:c>
-      <x:c r="G5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
-      </x:c>
-      <x:c r="H5" s="278" t="str">
-        <x:v>基準BL-2026-09-24。CHG-AUTH-20260928-01の改訂文書はVer.2.6、変更承認待ち。</x:v>
-      </x:c>
+        <x:v>基準BL-2026-09-24。既存AUTH/MENU/DB変更及びCHG-BATCH-20260930-01を含む。Document Versionは各行を正とする。正式承認は別途記録。
+CHG-ACTOR-20261007-01を反映。</x:v>
+      </x:c>
+      <x:c r="B5" s="278"/>
+      <x:c r="C5" s="278"/>
+      <x:c r="D5" s="278"/>
+      <x:c r="E5" s="278"/>
+      <x:c r="F5" s="278"/>
+      <x:c r="G5" s="278"/>
+      <x:c r="H5" s="278"/>
       <x:c r="I5"/>
       <x:c r="J5"/>
       <x:c r="K5"/>
@@ -3898,7 +3999,7 @@
         <x:v>基本設計書総合管理</x:v>
       </x:c>
       <x:c r="E8" s="283" t="str">
-        <x:v>Ver.2.8</x:v>
+        <x:v>Ver.2.11</x:v>
       </x:c>
       <x:c r="F8" s="283" t="str">
         <x:v>修正済</x:v>
@@ -4228,13 +4329,13 @@
         <x:v>従業員と部門_API基本設計書</x:v>
       </x:c>
       <x:c r="E19" s="282" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F19" s="282" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G19" s="282" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H19" s="282" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4288,13 +4389,13 @@
         <x:v>タスクとファイル_API基本設計書</x:v>
       </x:c>
       <x:c r="E21" s="282" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="F21" s="282" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G21" s="282" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H21" s="282" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4318,7 +4419,7 @@
         <x:v>日報と通知_API基本設計書</x:v>
       </x:c>
       <x:c r="E22" s="283" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F22" s="283" t="str">
         <x:v>修正済</x:v>
@@ -4348,7 +4449,7 @@
         <x:v>DB基本設計書</x:v>
       </x:c>
       <x:c r="E23" s="282" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.9</x:v>
       </x:c>
       <x:c r="F23" s="282" t="str">
         <x:v>修正済</x:v>
@@ -4408,7 +4509,7 @@
         <x:v>トランザクションと排他_基本設計書</x:v>
       </x:c>
       <x:c r="E25" s="282" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.8</x:v>
       </x:c>
       <x:c r="F25" s="282" t="str">
         <x:v>修正済</x:v>
@@ -4498,13 +4599,13 @@
         <x:v>バッチ非機能運用_基本設計書</x:v>
       </x:c>
       <x:c r="E28" s="283" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F28" s="283" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G28" s="283" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H28" s="283" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4665,7 +4766,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
-        <x:v>Ver.2.7</x:v>
+        <x:v>Ver.2.11</x:v>
       </x:c>
       <x:c r="C4" s="160"/>
       <x:c r="D4" s="160"/>
@@ -4674,7 +4775,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="G4" s="72" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="H4" s="160"/>
       <x:c r="I4" s="160"/>
@@ -5337,7 +5438,7 @@
         <x:v>PERM-EMP-WRITE</x:v>
       </x:c>
       <x:c r="F23" s="76" t="str">
-        <x:v>employees,users,tasks,project_members,refresh_tokens,operation_logs / Redis</x:v>
+        <x:v>employees,users,tasks,task_histories,notifications,projects,project_members,refresh_tokens,operation_logs / Redis</x:v>
       </x:c>
       <x:c r="G23" s="76" t="str">
         <x:v>BR-EMP-003, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
@@ -6591,7 +6692,7 @@
         <x:v>PERM-TASK-READ</x:v>
       </x:c>
       <x:c r="F56" s="76" t="str">
-        <x:v>tasks,task_comments,task_attachments,task_histories,task_tags</x:v>
+        <x:v>tasks,task_comments,task_attachments,task_histories,task_tags,users,employees</x:v>
       </x:c>
       <x:c r="G56" s="76" t="str">
         <x:v>BR-TASK-004</x:v>
@@ -6629,7 +6730,7 @@
         <x:v>PERM-TASK-WRITE</x:v>
       </x:c>
       <x:c r="F57" s="76" t="str">
-        <x:v>tasks,project_members,task_histories,notifications,task_tags</x:v>
+        <x:v>tasks,project_members,task_histories,notifications,task_tags,users,employees</x:v>
       </x:c>
       <x:c r="G57" s="76" t="str">
         <x:v>BR-TASK-001, BR-TASK-002, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
@@ -6667,7 +6768,7 @@
         <x:v>PERM-TASK-WRITE</x:v>
       </x:c>
       <x:c r="F58" s="76" t="str">
-        <x:v>tasks,task_histories,notifications,task_tags</x:v>
+        <x:v>tasks,task_histories,notifications,task_tags,projects,operation_logs,users</x:v>
       </x:c>
       <x:c r="G58" s="76" t="str">
         <x:v>BR-TASK-001, BR-TASK-002, BR-DATA-001, BR-LOG-001</x:v>
@@ -6705,7 +6806,7 @@
         <x:v>PERM-TASK-WRITE / PERM-TASK-PROGRESS / PERM-TASK-APPROVE</x:v>
       </x:c>
       <x:c r="F59" s="76" t="str">
-        <x:v>tasks,task_histories,notifications,projects</x:v>
+        <x:v>tasks,task_histories,notifications,projects,users</x:v>
       </x:c>
       <x:c r="G59" s="76" t="str">
         <x:v>BR-TASK-003, BR-DATA-001, BR-LOG-001</x:v>
@@ -6743,7 +6844,7 @@
         <x:v>PERM-TASK-PROGRESS</x:v>
       </x:c>
       <x:c r="F60" s="76" t="str">
-        <x:v>tasks,task_histories</x:v>
+        <x:v>tasks,task_histories,projects,operation_logs,users</x:v>
       </x:c>
       <x:c r="G60" s="76" t="str">
         <x:v>BR-TASK-003, BR-DATA-001, BR-LOG-001</x:v>
@@ -6781,7 +6882,7 @@
         <x:v>PERM-TASK-READ（PJ Member）</x:v>
       </x:c>
       <x:c r="F61" s="76" t="str">
-        <x:v>task_comments,tasks</x:v>
+        <x:v>task_comments,tasks,notifications,operation_logs,users,employees</x:v>
       </x:c>
       <x:c r="G61" s="76" t="str">
         <x:v>BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
@@ -6857,7 +6958,7 @@
         <x:v>PERM-FILE-WRITE</x:v>
       </x:c>
       <x:c r="F63" s="76" t="str">
-        <x:v>task_attachments,tasks,operation_logs</x:v>
+        <x:v>task_attachments,tasks,operation_logs,users</x:v>
       </x:c>
       <x:c r="G63" s="76" t="str">
         <x:v>BR-FILE-001, BR-FILE-002, BR-DATA-001, BR-API-001, BR-LOG-001</x:v>
@@ -7207,7 +7308,7 @@
         <x:v>20／37の通知定義、18／32の共通例外</x:v>
       </x:c>
       <x:c r="H76" s="272" t="str">
-        <x:v>Batch詳細設計 / UT-BATCH-001 / IT-BATCH-001</x:v>
+        <x:v>バッチ詳細設計／01_BATCH-001_期限前Task通知詳細設計書 Ver.1.1／UT-001～044／IT-BATCH-001</x:v>
       </x:c>
       <x:c r="I76" s="272" t="str">
         <x:v>多重起動時のみBATCH-5001。正常実行時はErrorなし。16／28 BR-BATCH-001、18／32 Batch排他例外、20／37 Batch起動制御を参照。処理開始後の失敗は20／37の各Batch定義に従う。</x:v>
@@ -7441,13 +7542,13 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="72" t="str">
-        <x:v>Ver.2.7</x:v>
+        <x:v>Ver.2.11</x:v>
       </x:c>
       <x:c r="C4" s="71" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D4" s="72" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="E4" s="72"/>
       <x:c r="F4" s="72"/>
@@ -7768,6 +7869,26 @@
         <x:v>確定</x:v>
       </x:c>
     </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="266" t="str">
+        <x:v>DEC-011</x:v>
+      </x:c>
+      <x:c r="B18" s="266" t="str">
+        <x:v>DB Migration採番</x:v>
+      </x:c>
+      <x:c r="C18" s="266" t="str">
+        <x:v>DB-DD-01=V101～V110、DB-DD-02=V201～V210、DB-DD-03=V301～V310。撤回番号は再利用せず、空SQLは作成しない。</x:v>
+      </x:c>
+      <x:c r="D18" s="266" t="str">
+        <x:v>複数担当者のVersion衝突と実行順序の差異を防止する。</x:v>
+      </x:c>
+      <x:c r="E18" s="266" t="str">
+        <x:v>DB-DD-01～03／詳細設計書書写規範</x:v>
+      </x:c>
+      <x:c r="F18" s="266" t="str">
+        <x:v>確定</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="290" t="str">
         <x:v>変更ID</x:v>
@@ -7845,6 +7966,126 @@
         <x:v>基準BL-2026-09-24／承認後にBaseline更新</x:v>
       </x:c>
       <x:c r="F22" s="266" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="90" customHeight="1">
+      <x:c r="A23" s="266" t="str">
+        <x:v>CHG-ACTOR-20261007-01</x:v>
+      </x:c>
+      <x:c r="B23" s="266" t="str">
+        <x:v>Task報告者・操作者ID明確化</x:v>
+      </x:c>
+      <x:c r="C23" s="266" t="str">
+        <x:v>正本：tasks.reporter_id→employees.id。task_comments.user_id／task_attachments.uploaded_by／task_histories.changed_by→users.id。全て認証情報からServer設定しClient指定不可。</x:v>
+      </x:c>
+      <x:c r="D23" s="266" t="str">
+        <x:v>業務上の報告者と認証アカウント上の操作者を分離し、退職・停止後も履歴を保持する。</x:v>
+      </x:c>
+      <x:c r="E23" s="266" t="str">
+        <x:v>基本設計11・13・15・17／DB-DD-02</x:v>
+      </x:c>
+      <x:c r="F23" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="78" customHeight="1">
+      <x:c r="A24" s="266" t="str">
+        <x:v>影響調査</x:v>
+      </x:c>
+      <x:c r="B24" s="266" t="str">
+        <x:v>変更範囲</x:v>
+      </x:c>
+      <x:c r="C24" s="266" t="str">
+        <x:v>物理外鍵は追加しない。API設定元、Transaction、関連Table、ER・論理参照、UT観点を同期する。</x:v>
+      </x:c>
+      <x:c r="D24" s="266" t="str">
+        <x:v>退職処理で生成するTask履歴は、対象社員ではなく操作管理者のusers.idをchanged_byに設定する。</x:v>
+      </x:c>
+      <x:c r="E24" s="266" t="str">
+        <x:v>00追跡Matrix・11 API-EMP-005・13 API-TASK・15 DB・17 TX-005</x:v>
+      </x:c>
+      <x:c r="F24" s="266" t="str">
+        <x:v>調査済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="78" customHeight="1">
+      <x:c r="A25" s="266" t="str">
+        <x:v>承認管理</x:v>
+      </x:c>
+      <x:c r="B25" s="266" t="str">
+        <x:v>変更後Review</x:v>
+      </x:c>
+      <x:c r="C25" s="266" t="str">
+        <x:v>PR8のDB-DD-02は本決定に従いER、Column参照、孤児検査SQL、UTを修正する。</x:v>
+      </x:c>
+      <x:c r="D25" s="266" t="str">
+        <x:v>基本設計の変更指示と成果物の正式承認を区別する。</x:v>
+      </x:c>
+      <x:c r="E25" s="266" t="str">
+        <x:v>基準BL-2026-09-24／承認後にBaseline更新</x:v>
+      </x:c>
+      <x:c r="F25" s="266" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="90" customHeight="1">
+      <x:c r="A26" s="266" t="str">
+        <x:v>CHG-MIG-20261007-01</x:v>
+      </x:c>
+      <x:c r="B26" s="266" t="str">
+        <x:v>Flyway Version帯明確化</x:v>
+      </x:c>
+      <x:c r="C26" s="266" t="str">
+        <x:v>正本：DEC-011。DB-DD-02はV201～V208をprojects、project_members、tasks、comments、attachments、histories、tags、indexesの順に割当。V209～V210は予約。</x:v>
+      </x:c>
+      <x:c r="D26" s="266" t="str">
+        <x:v>DB-DD-01のV101～V110と衝突せず、DB-DD-03用V301～V310を確保する。</x:v>
+      </x:c>
+      <x:c r="E26" s="266" t="str">
+        <x:v>詳細設計書書写規範／DB-DD-01～03</x:v>
+      </x:c>
+      <x:c r="F26" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="78" customHeight="1">
+      <x:c r="A27" s="266" t="str">
+        <x:v>影響調査</x:v>
+      </x:c>
+      <x:c r="B27" s="266" t="str">
+        <x:v>変更範囲</x:v>
+      </x:c>
+      <x:c r="C27" s="266" t="str">
+        <x:v>DB-DD-01のV108撤回・欠番維持とV109／V110は変更しない。DB-DD-02の未採番名のみV201～V208へ置換する。</x:v>
+      </x:c>
+      <x:c r="D27" s="266" t="str">
+        <x:v>新規TableやAlter追加は対応帯の次番を使用し、使い切った場合はProject Leaderが新帯を割り当てる。</x:v>
+      </x:c>
+      <x:c r="E27" s="266" t="str">
+        <x:v>WR-ID-010／CK-DB-012／各DB改訂履歴</x:v>
+      </x:c>
+      <x:c r="F27" s="266" t="str">
+        <x:v>調査済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="78" customHeight="1">
+      <x:c r="A28" s="266" t="str">
+        <x:v>承認管理</x:v>
+      </x:c>
+      <x:c r="B28" s="266" t="str">
+        <x:v>変更後Review</x:v>
+      </x:c>
+      <x:c r="C28" s="266" t="str">
+        <x:v>PR8でV201～V208の重複、依存順、Flyway validate、実際SQLファイル名を確認する。</x:v>
+      </x:c>
+      <x:c r="D28" s="266" t="str">
+        <x:v>番号割当ての確定とPR成果物の承認を区別する。</x:v>
+      </x:c>
+      <x:c r="E28" s="266" t="str">
+        <x:v>基準BL-2026-09-24／承認後にBaseline更新</x:v>
+      </x:c>
+      <x:c r="F28" s="266" t="str">
         <x:v>承認待ち</x:v>
       </x:c>
     </x:row>

--- a/基本設計/00_基本設計書総合管理.xlsx
+++ b/基本設計/00_基本設計書総合管理.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R695279477bad40e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rff1d8bd31f8949a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R54a97e8d7a9244db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="Rca30d8a25b5d4423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="Ra5ad7404b7f44989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R15a5a987134f432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="Re1345a45099a459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="R7d538cdaedca49ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb079a3f9a7b64a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rd99731aaa55f48b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R5f1e37a71066416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="Rf7da1643f6d84210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="R8ccae971063e4953"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R6fd71e9b5f994e94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R5f287d3ce7a14578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="Re56fcfb7f8ed45a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1561,7 +1561,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="265" t="str">
-        <x:v>Ver.2.12</x:v>
+        <x:v>Ver.2.13</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1598,7 +1598,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="270" t="str">
-        <x:v>Ver.2.12</x:v>
+        <x:v>Ver.2.13</x:v>
       </x:c>
       <x:c r="E13" s="222"/>
       <x:c r="F13" s="222"/>
@@ -1695,12 +1695,13 @@
       <x:c r="K18"/>
       <x:c r="L18"/>
     </x:row>
-    <x:row r="19" ht="55" customHeight="1">
+    <x:row r="19" ht="104" customHeight="1">
       <x:c r="A19"/>
       <x:c r="B19" s="265" t="str">
         <x:v>基準Baseline：BL-2026-09-24。CHG-AUTH-20260928-01／CHG-MENU-20260929-01／CHG-DB-20260929-01を反映。物理外鍵非採用。正式承認・次Baseline登録は別途。 CHG-BATCH-20260930-01：Batch実行規約・通知ID採番を反映。
 CHG-ACTOR-20261007-01：Task関連の報告者・操作者ID定義を11・13・15・17へ反映。
-CHG-MIG-20261007-01：DB詳細設計ごとのFlyway Version帯を確定。正式Baseline更新は承認後とする。</x:v>
+CHG-MIG-20261007-01：DB詳細設計ごとのFlyway Version帯を確定。正式Baseline更新は承認後とする。
+研修適用（DB-DD-01）：BL-2026-09-24／CHG-DB-20260929-01／CHG-MIG-20261007-01／参照基準日2026-10-08。学員は本欄から転記し、独自判断で変更しない。</x:v>
       </x:c>
       <x:c r="C19"/>
       <x:c r="D19"/>
@@ -1860,7 +1861,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.12    改訂日：2026-10-08    基準Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.13    改訂日：2026-10-08    基準Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="72"/>
       <x:c r="C4" s="72"/>
@@ -2546,15 +2547,31 @@
         <x:v>14・15・16・20の通知関連仕様を整合。基準Baselineは維持。</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-      <x:c r="D30"/>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
+    <x:row r="30" ht="58" hidden="0" customHeight="1">
+      <x:c r="A30" s="266" t="str">
+        <x:v>Ver.2.13</x:v>
+      </x:c>
+      <x:c r="B30" s="266" t="str">
+        <x:v>2026-10-08</x:v>
+      </x:c>
+      <x:c r="C30" s="266" t="str">
+        <x:v>CHG-TRACE-20261008-01：DB詳細設計の関連API逆引き規則と、DB-DD-01の研修適用Baseline／Change ID／参照基準日を確定。</x:v>
+      </x:c>
+      <x:c r="D30" s="266" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E30" s="266" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F30" s="266" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G30" s="266" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H30" s="266" t="str">
+        <x:v>00／07、01E、詳細設計書書写規範を同期。基準Baselineは維持。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8209,7 +8226,7 @@
         <x:v>共通/Authは10、Domainは各分冊</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="36" customHeight="1">
+    <x:row r="13" ht="86" customHeight="1">
       <x:c r="A13" s="282" t="str">
         <x:v>DB構造</x:v>
       </x:c>
@@ -8217,7 +8234,7 @@
         <x:v>15_DB基本設計書</x:v>
       </x:c>
       <x:c r="C13" s="282" t="str">
-        <x:v>API Mappingから参照</x:v>
+        <x:v>関連APIは10～14／22_API処理・権限の関連TableからTable名完全一致で逆引きし、該当API IDを全件・昇順で記載する。Redis／File等の非DB資源とAPI Group名は対象外。全体確認は00／05_トレーサビリティを使用する。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">

--- a/基本設計/00_基本設計書総合管理.xlsx
+++ b/基本設計/00_基本設計書総合管理.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb079a3f9a7b64a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rd99731aaa55f48b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R5f1e37a71066416d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="Rf7da1643f6d84210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="R8ccae971063e4953"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R6fd71e9b5f994e94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="R5f287d3ce7a14578"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="Re56fcfb7f8ed45a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rd2cfd231c7e6480f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R189904c9e2074e46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_用語集" sheetId="4" r:id="R35262a234ca34127"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_前提条件" sheetId="5" r:id="R032c5f5c96e04da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_文書一覧" sheetId="49" r:id="Rf48238bf95ce4d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_トレーサビリティ" sheetId="50" r:id="R61cf663987934a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_設計決定事項" sheetId="51" r:id="Reb7bd3ebe69e4c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_設計正本対応" sheetId="52" r:id="R19aca268c71b48e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1561,7 +1561,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="265" t="str">
-        <x:v>Ver.2.13</x:v>
+        <x:v>Ver.2.14</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1598,7 +1598,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="270" t="str">
-        <x:v>Ver.2.13</x:v>
+        <x:v>Ver.2.14</x:v>
       </x:c>
       <x:c r="E13" s="222"/>
       <x:c r="F13" s="222"/>
@@ -1616,7 +1616,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="270" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="E14" s="222"/>
       <x:c r="F14" s="222"/>
@@ -1861,7 +1861,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="275" t="str">
-        <x:v>版数：Ver.2.13    改訂日：2026-10-08    基準Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.14    改訂日：2026-10-15    Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="72"/>
       <x:c r="C4" s="72"/>
@@ -2571,6 +2571,32 @@
       </x:c>
       <x:c r="H30" s="266" t="str">
         <x:v>00／07、01E、詳細設計書書写規範を同期。基準Baselineは維持。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="266" t="str">
+        <x:v>Ver.2.14</x:v>
+      </x:c>
+      <x:c r="B31" s="266" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C31" s="266" t="str">
+        <x:v>API-EMP-007の0件Response明確化に伴い05・11の文書版数と承認状態を更新。</x:v>
+      </x:c>
+      <x:c r="D31" s="266" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E31" s="266" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F31" s="266" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G31" s="266" t="str">
+        <x:v>変更承認待ち</x:v>
+      </x:c>
+      <x:c r="H31" s="266" t="str">
+        <x:v>BL-2026-09-24の変更承認待ち。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4166,13 +4192,13 @@
         <x:v>従業員と部門_画面基本設計書</x:v>
       </x:c>
       <x:c r="E13" s="282" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F13" s="282" t="str">
         <x:v>修正済</x:v>
       </x:c>
       <x:c r="G13" s="282" t="str">
-        <x:v>Review中</x:v>
+        <x:v>変更承認待ち</x:v>
       </x:c>
       <x:c r="H13" s="282" t="str">
         <x:v>BL-2026-09-24</x:v>
@@ -4346,7 +4372,7 @@
         <x:v>従業員と部門_API基本設計書</x:v>
       </x:c>
       <x:c r="E19" s="282" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="F19" s="282" t="str">
         <x:v>修正済</x:v>
